--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
@@ -827,7 +827,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie "No ano, por sócio" e "Lucro e distribuição por trimestre" e use o prompt "Explicar o mês ao sócio" da biblioteca do kit para preparar a conversa entre os sócios.</t>
+          <t>Copie "No ano, por sócio" e "Lucro e distribuição por trimestre" e use o prompt "Caixa 06 · Separar o que é do escritório e o que é pessoal" da biblioteca do kit para preparar a conversa entre os sócios.</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -931,9 +931,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · Pró-labore e retiradas · "&amp;Config!B6&amp;" de "&amp;Config!B5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Pró-labore e retiradas · Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -978,27 +978,27 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>Config!$C$20</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>SUM(H9:H14)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>SUM(I9:I14)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="17">
         <f>SUM(G20:G25)</f>
-        <v/>
+        <v>5060</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="18">
         <f>SUM(J20:J25)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J5" s="14" t="n"/>
     </row>
@@ -1062,87 +1062,87 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21">
+      <c r="A9" s="21" t="str">
         <f>IF(Config!$A$14="","",Config!$A$14)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="B9" s="22">
         <f>IF(Config!$A$14="","",Config!$C$14)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="C9" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Pró-labore",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D9" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Retirada extra",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E9" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Despesa pessoal paga pelo escritório",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F9" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Devolução ao escritório",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" s="23">
         <f>IF(Config!$A$14="","",C9+D9+E9-F9+G9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I9" s="22">
         <f>IF(Config!$A$14="","",D9+E9-F9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="24">
+        <v>0</v>
+      </c>
+      <c r="J9" s="24" t="str">
         <f>IF(Config!$A$14="","",IF(I9&gt;0,"Acima do combinado",IF(C9&lt;B9,"Pró-labore ainda não pago por completo","Conforme o combinado")))</f>
-        <v/>
+        <v>Pró-labore ainda não pago por completo</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21">
+      <c r="A10" s="21" t="str">
         <f>IF(Config!$A$15="","",Config!$A$15)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="B10" s="22">
         <f>IF(Config!$A$15="","",Config!$C$15)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="C10" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Pró-labore",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D10" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Retirada extra",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E10" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Despesa pessoal paga pelo escritório",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F10" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Devolução ao escritório",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="23">
         <f>IF(Config!$A$15="","",C10+D10+E10-F10+G10)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I10" s="22">
         <f>IF(Config!$A$15="","",D10+E10-F10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="24">
+        <v>0</v>
+      </c>
+      <c r="J10" s="24" t="str">
         <f>IF(Config!$A$15="","",IF(I10&gt;0,"Acima do combinado",IF(C10&lt;B10,"Pró-labore ainda não pago por completo","Conforme o combinado")))</f>
-        <v/>
+        <v>Pró-labore ainda não pago por completo</v>
       </c>
     </row>
     <row r="11">
@@ -1380,87 +1380,87 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21">
+      <c r="A20" s="21" t="str">
         <f>IF(Config!$A$14="","",Config!$A$14)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="B20" s="22">
         <f>IF(Config!$A$14="","",Config!$C$14*Config!$B$7)</f>
-        <v/>
+        <v>54000</v>
       </c>
       <c r="C20" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Pró-labore",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="D20" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Retirada extra",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="E20" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Despesa pessoal paga pelo escritório",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>1440</v>
       </c>
       <c r="F20" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Devolução ao escritório",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>480</v>
       </c>
       <c r="G20" s="23">
         <f>IF(Config!$A$14="","",D20+E20-F20)</f>
-        <v/>
+        <v>2960</v>
       </c>
       <c r="H20" s="22">
         <f>IF(Config!$A$14="","",SUM($G$32:$G$35)*Config!$B$14)</f>
-        <v/>
+        <v>6452.25</v>
       </c>
       <c r="I20" s="22">
         <f>IF(Config!$A$14="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$14,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>6452</v>
       </c>
       <c r="J20" s="23">
         <f>IF(Config!$A$14="","",IF(ABS(H20-I20)&lt;1,0,H20-I20))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21">
+      <c r="A21" s="21" t="str">
         <f>IF(Config!$A$15="","",Config!$A$15)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="B21" s="22">
         <f>IF(Config!$A$15="","",Config!$C$15*Config!$B$7)</f>
-        <v/>
+        <v>54000</v>
       </c>
       <c r="C21" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Pró-labore",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="D21" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Retirada extra",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="E21" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Despesa pessoal paga pelo escritório",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="F21" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Devolução ao escritório",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G21" s="23">
         <f>IF(Config!$A$15="","",D21+E21-F21)</f>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="H21" s="22">
         <f>IF(Config!$A$15="","",SUM($G$32:$G$35)*Config!$B$15)</f>
-        <v/>
+        <v>6452.25</v>
       </c>
       <c r="I21" s="22">
         <f>IF(Config!$A$15="","",SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$B$5:$B$404,Config!$A$15,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$G$5:$G$404,"&lt;="&amp;Config!$B$7,Retiradas!$H$5:$H$404,Config!$B$5))</f>
-        <v/>
+        <v>6453</v>
       </c>
       <c r="J21" s="23">
         <f>IF(Config!$A$15="","",IF(ABS(H21-I21)&lt;1,0,H21-I21))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1707,35 +1707,35 @@
       </c>
       <c r="B32" s="22">
         <f>SUM('Resultado mensal'!B5:B7)</f>
-        <v/>
+        <v>72710</v>
       </c>
       <c r="C32" s="22">
         <f>SUM('Resultado mensal'!C5:C7)</f>
-        <v/>
+        <v>26088</v>
       </c>
       <c r="D32" s="22">
         <f>SUM('Resultado mensal'!D5:D7)</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="E32" s="22">
         <f>SUM('Resultado mensal'!E5:E7)</f>
-        <v/>
-      </c>
-      <c r="F32" s="24">
+        <v>10622</v>
+      </c>
+      <c r="F32" s="24" t="str">
         <f>IF(Config!$B$7&gt;3,"Sim","Em andamento")</f>
-        <v/>
+        <v>Sim</v>
       </c>
       <c r="G32" s="23">
         <f>IF(AND(F32="Sim",E32&gt;=Config!$B$10),E32*Config!$B$9,0)</f>
-        <v/>
+        <v>5311</v>
       </c>
       <c r="H32" s="22">
         <f>SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$F$5:$F$404,A32,Retiradas!$H$5:$H$404,Config!$B$5)</f>
-        <v/>
+        <v>5311</v>
       </c>
       <c r="I32" s="22">
         <f>IF(ABS(G32-H32)&lt;1,0,G32-H32)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1746,35 +1746,35 @@
       </c>
       <c r="B33" s="22">
         <f>SUM('Resultado mensal'!B8:B10)</f>
-        <v/>
+        <v>78300</v>
       </c>
       <c r="C33" s="22">
         <f>SUM('Resultado mensal'!C8:C10)</f>
-        <v/>
+        <v>27113</v>
       </c>
       <c r="D33" s="22">
         <f>SUM('Resultado mensal'!D8:D10)</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="E33" s="22">
         <f>SUM('Resultado mensal'!E8:E10)</f>
-        <v/>
-      </c>
-      <c r="F33" s="24">
+        <v>15187</v>
+      </c>
+      <c r="F33" s="24" t="str">
         <f>IF(Config!$B$7&gt;6,"Sim","Em andamento")</f>
-        <v/>
+        <v>Sim</v>
       </c>
       <c r="G33" s="23">
         <f>IF(AND(F33="Sim",E33&gt;=Config!$B$10),E33*Config!$B$9,0)</f>
-        <v/>
+        <v>7593.5</v>
       </c>
       <c r="H33" s="22">
         <f>SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$F$5:$F$404,A33,Retiradas!$H$5:$H$404,Config!$B$5)</f>
-        <v/>
+        <v>7594</v>
       </c>
       <c r="I33" s="22">
         <f>IF(ABS(G33-H33)&lt;1,0,G33-H33)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1785,35 +1785,35 @@
       </c>
       <c r="B34" s="22">
         <f>SUM('Resultado mensal'!B11:B13)</f>
-        <v/>
+        <v>61580</v>
       </c>
       <c r="C34" s="22">
         <f>SUM('Resultado mensal'!C11:C13)</f>
-        <v/>
+        <v>23741</v>
       </c>
       <c r="D34" s="22">
         <f>SUM('Resultado mensal'!D11:D13)</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="E34" s="22">
         <f>SUM('Resultado mensal'!E11:E13)</f>
-        <v/>
-      </c>
-      <c r="F34" s="24">
+        <v>1839</v>
+      </c>
+      <c r="F34" s="24" t="str">
         <f>IF(Config!$B$7&gt;9,"Sim","Em andamento")</f>
-        <v/>
+        <v>Em andamento</v>
       </c>
       <c r="G34" s="23">
         <f>IF(AND(F34="Sim",E34&gt;=Config!$B$10),E34*Config!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H34" s="22">
         <f>SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$F$5:$F$404,A34,Retiradas!$H$5:$H$404,Config!$B$5)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I34" s="22">
         <f>IF(ABS(G34-H34)&lt;1,0,G34-H34)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1824,35 +1824,35 @@
       </c>
       <c r="B35" s="22">
         <f>SUM('Resultado mensal'!B14:B16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C35" s="22">
         <f>SUM('Resultado mensal'!C14:C16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D35" s="22">
         <f>SUM('Resultado mensal'!D14:D16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E35" s="22">
         <f>SUM('Resultado mensal'!E14:E16)</f>
-        <v/>
-      </c>
-      <c r="F35" s="24">
+        <v>0</v>
+      </c>
+      <c r="F35" s="24" t="str">
         <f>IF(Config!$B$7&gt;12,"Sim","Em andamento")</f>
-        <v/>
+        <v>Em andamento</v>
       </c>
       <c r="G35" s="23">
         <f>IF(AND(F35="Sim",E35&gt;=Config!$B$10),E35*Config!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H35" s="22">
         <f>SUMIFS(Retiradas!$E$5:$E$404,Retiradas!$C$5:$C$404,"Distribuição de lucro",Retiradas!$F$5:$F$404,A35,Retiradas!$H$5:$H$404,Config!$B$5)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I35" s="22">
         <f>IF(ABS(G35-H35)&lt;1,0,G35-H35)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B7" s="24">
         <f>MATCH(B6,$H$5:$H$16,0)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="B8" s="24">
         <f>ROUNDUP(B7/3,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H8" s="29" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="B20" s="34">
         <f>SUM(B14:B19)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C20" s="35">
         <f>SUM(C14:C19)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="D20" s="36">
         <f>IF(ROUND(B20,4)=1,"","A participação deve somar 100 %")</f>
@@ -2329,18 +2329,18 @@
         </is>
       </c>
       <c r="B5" s="32" t="n">
-        <v>33660</v>
+        <v>21050</v>
       </c>
       <c r="C5" s="32" t="n">
         <v>8408</v>
       </c>
       <c r="D5" s="37">
         <f>IF(AND(B5="",C5=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E5" s="37">
         <f>B5-C5-D5</f>
-        <v/>
+        <v>642</v>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
@@ -2355,18 +2355,18 @@
         </is>
       </c>
       <c r="B6" s="32" t="n">
-        <v>14000</v>
+        <v>23070</v>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9793</v>
+        <v>9204</v>
       </c>
       <c r="D6" s="37">
         <f>IF(AND(B6="",C6=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E6" s="37">
         <f>B6-C6-D6</f>
-        <v/>
+        <v>1866</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2381,18 +2381,18 @@
         </is>
       </c>
       <c r="B7" s="32" t="n">
-        <v>19560</v>
+        <v>28590</v>
       </c>
       <c r="C7" s="32" t="n">
-        <v>8400</v>
+        <v>8476</v>
       </c>
       <c r="D7" s="37">
         <f>IF(AND(B7="",C7=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E7" s="37">
         <f>B7-C7-D7</f>
-        <v/>
+        <v>8114</v>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
@@ -2407,18 +2407,18 @@
         </is>
       </c>
       <c r="B8" s="32" t="n">
-        <v>20420</v>
+        <v>19760</v>
       </c>
       <c r="C8" s="32" t="n">
-        <v>8605</v>
+        <v>9327</v>
       </c>
       <c r="D8" s="37">
         <f>IF(AND(B8="",C8=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E8" s="37">
         <f>B8-C8-D8</f>
-        <v/>
+        <v>-1567</v>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
@@ -2433,18 +2433,18 @@
         </is>
       </c>
       <c r="B9" s="32" t="n">
-        <v>19200</v>
+        <v>31120</v>
       </c>
       <c r="C9" s="32" t="n">
-        <v>8574</v>
+        <v>8701</v>
       </c>
       <c r="D9" s="37">
         <f>IF(AND(B9="",C9=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E9" s="37">
         <f>B9-C9-D9</f>
-        <v/>
+        <v>10419</v>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
@@ -2459,18 +2459,18 @@
         </is>
       </c>
       <c r="B10" s="32" t="n">
-        <v>25970</v>
+        <v>27420</v>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8346</v>
+        <v>9085</v>
       </c>
       <c r="D10" s="37">
         <f>IF(AND(B10="",C10=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E10" s="37">
         <f>B10-C10-D10</f>
-        <v/>
+        <v>6335</v>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
@@ -2485,18 +2485,18 @@
         </is>
       </c>
       <c r="B11" s="32" t="n">
-        <v>30170</v>
+        <v>29460</v>
       </c>
       <c r="C11" s="32" t="n">
-        <v>8673</v>
+        <v>9004</v>
       </c>
       <c r="D11" s="37">
         <f>IF(AND(B11="",C11=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E11" s="37">
         <f>B11-C11-D11</f>
-        <v/>
+        <v>8456</v>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
@@ -2511,18 +2511,18 @@
         </is>
       </c>
       <c r="B12" s="32" t="n">
-        <v>26660</v>
+        <v>26900</v>
       </c>
       <c r="C12" s="32" t="n">
-        <v>9474</v>
+        <v>9417</v>
       </c>
       <c r="D12" s="37">
         <f>IF(AND(B12="",C12=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E12" s="37">
         <f>B12-C12-D12</f>
-        <v/>
+        <v>5483</v>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
@@ -2537,18 +2537,18 @@
         </is>
       </c>
       <c r="B13" s="32" t="n">
-        <v>10800</v>
+        <v>5220</v>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5970</v>
+        <v>5320</v>
       </c>
       <c r="D13" s="37">
         <f>IF(AND(B13="",C13=""),0,Config!$C$20)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="E13" s="37">
         <f>B13-C13-D13</f>
-        <v/>
+        <v>-12100</v>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
@@ -2566,11 +2566,11 @@
       <c r="C14" s="32" t="n"/>
       <c r="D14" s="37">
         <f>IF(AND(B14="",C14=""),0,Config!$C$20)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E14" s="37">
         <f>B14-C14-D14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
@@ -2588,11 +2588,11 @@
       <c r="C15" s="32" t="n"/>
       <c r="D15" s="37">
         <f>IF(AND(B15="",C15=""),0,Config!$C$20)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E15" s="37">
         <f>B15-C15-D15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
@@ -2610,11 +2610,11 @@
       <c r="C16" s="32" t="n"/>
       <c r="D16" s="37">
         <f>IF(AND(B16="",C16=""),0,Config!$C$20)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E16" s="37">
         <f>B16-C16-D16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>Saídas sem sócios = Saiu no mês (Painel da planilha 09) menos pró-labore, retiradas extras, distribuição de lucro e despesas pessoais dos sócios. Meses não fechados ficam em branco.</t>
+          <t>Entradas = Entrou no mês (Painel da planilha 09) menos devoluções dos sócios (Outras entradas). Saídas sem sócios = Saiu no mês menos pró-labore, retiradas extras, distribuição de lucro e despesas pessoais dos sócios. Meses não fechados ficam em branco (setembro: até 11/09).</t>
         </is>
       </c>
     </row>
@@ -2744,11 +2744,11 @@
       <c r="F5" s="28" t="inlineStr"/>
       <c r="G5" s="24">
         <f>IF(A5="","",MONTH(A5))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H5" s="24">
         <f>IF(A5="","",YEAR(A5))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="6">
@@ -2776,11 +2776,11 @@
       <c r="F6" s="28" t="inlineStr"/>
       <c r="G6" s="24">
         <f>IF(A6="","",MONTH(A6))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H6" s="24">
         <f>IF(A6="","",YEAR(A6))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="7">
@@ -2808,11 +2808,11 @@
       <c r="F7" s="28" t="inlineStr"/>
       <c r="G7" s="24">
         <f>IF(A7="","",MONTH(A7))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H7" s="24">
         <f>IF(A7="","",YEAR(A7))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="8">
@@ -2840,11 +2840,11 @@
       <c r="F8" s="28" t="inlineStr"/>
       <c r="G8" s="24">
         <f>IF(A8="","",MONTH(A8))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H8" s="24">
         <f>IF(A8="","",YEAR(A8))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="9">
@@ -2872,11 +2872,11 @@
       <c r="F9" s="28" t="inlineStr"/>
       <c r="G9" s="24">
         <f>IF(A9="","",MONTH(A9))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H9" s="24">
         <f>IF(A9="","",YEAR(A9))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="10">
@@ -2904,11 +2904,11 @@
       <c r="F10" s="28" t="inlineStr"/>
       <c r="G10" s="24">
         <f>IF(A10="","",MONTH(A10))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H10" s="24">
         <f>IF(A10="","",YEAR(A10))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="11">
@@ -2936,11 +2936,11 @@
       <c r="F11" s="28" t="inlineStr"/>
       <c r="G11" s="24">
         <f>IF(A11="","",MONTH(A11))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H11" s="24">
         <f>IF(A11="","",YEAR(A11))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="12">
@@ -2968,11 +2968,11 @@
       <c r="F12" s="28" t="inlineStr"/>
       <c r="G12" s="24">
         <f>IF(A12="","",MONTH(A12))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H12" s="24">
         <f>IF(A12="","",YEAR(A12))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="13">
@@ -3000,11 +3000,11 @@
       <c r="F13" s="28" t="inlineStr"/>
       <c r="G13" s="24">
         <f>IF(A13="","",MONTH(A13))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H13" s="24">
         <f>IF(A13="","",YEAR(A13))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="14">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="E14" s="32" t="n">
-        <v>1155</v>
+        <v>2655</v>
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
@@ -3036,11 +3036,11 @@
       </c>
       <c r="G14" s="24">
         <f>IF(A14="","",MONTH(A14))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H14" s="24">
         <f>IF(A14="","",YEAR(A14))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="15">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="E15" s="32" t="n">
-        <v>1155</v>
+        <v>2656</v>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
@@ -3072,11 +3072,11 @@
       </c>
       <c r="G15" s="24">
         <f>IF(A15="","",MONTH(A15))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H15" s="24">
         <f>IF(A15="","",YEAR(A15))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="16">
@@ -3104,11 +3104,11 @@
       <c r="F16" s="28" t="inlineStr"/>
       <c r="G16" s="24">
         <f>IF(A16="","",MONTH(A16))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H16" s="24">
         <f>IF(A16="","",YEAR(A16))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="17">
@@ -3136,11 +3136,11 @@
       <c r="F17" s="28" t="inlineStr"/>
       <c r="G17" s="24">
         <f>IF(A17="","",MONTH(A17))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H17" s="24">
         <f>IF(A17="","",YEAR(A17))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="18">
@@ -3168,11 +3168,11 @@
       <c r="F18" s="28" t="inlineStr"/>
       <c r="G18" s="24">
         <f>IF(A18="","",MONTH(A18))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H18" s="24">
         <f>IF(A18="","",YEAR(A18))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="19">
@@ -3200,11 +3200,11 @@
       <c r="F19" s="28" t="inlineStr"/>
       <c r="G19" s="24">
         <f>IF(A19="","",MONTH(A19))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="H19" s="24">
         <f>IF(A19="","",YEAR(A19))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="20">
@@ -3232,11 +3232,11 @@
       <c r="F20" s="28" t="inlineStr"/>
       <c r="G20" s="24">
         <f>IF(A20="","",MONTH(A20))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="H20" s="24">
         <f>IF(A20="","",YEAR(A20))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="21">
@@ -3264,11 +3264,11 @@
       <c r="F21" s="28" t="inlineStr"/>
       <c r="G21" s="24">
         <f>IF(A21="","",MONTH(A21))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="H21" s="24">
         <f>IF(A21="","",YEAR(A21))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="22">
@@ -3296,11 +3296,11 @@
       <c r="F22" s="28" t="inlineStr"/>
       <c r="G22" s="24">
         <f>IF(A22="","",MONTH(A22))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H22" s="24">
         <f>IF(A22="","",YEAR(A22))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="23">
@@ -3328,11 +3328,11 @@
       <c r="F23" s="28" t="inlineStr"/>
       <c r="G23" s="24">
         <f>IF(A23="","",MONTH(A23))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H23" s="24">
         <f>IF(A23="","",YEAR(A23))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="24">
@@ -3360,11 +3360,11 @@
       <c r="F24" s="28" t="inlineStr"/>
       <c r="G24" s="24">
         <f>IF(A24="","",MONTH(A24))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H24" s="24">
         <f>IF(A24="","",YEAR(A24))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="25">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="E25" s="32" t="n">
-        <v>1016</v>
+        <v>3797</v>
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
@@ -3396,11 +3396,11 @@
       </c>
       <c r="G25" s="24">
         <f>IF(A25="","",MONTH(A25))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H25" s="24">
         <f>IF(A25="","",YEAR(A25))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="26">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="E26" s="32" t="n">
-        <v>1016</v>
+        <v>3797</v>
       </c>
       <c r="F26" s="28" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
       </c>
       <c r="G26" s="24">
         <f>IF(A26="","",MONTH(A26))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H26" s="24">
         <f>IF(A26="","",YEAR(A26))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="27">
@@ -3464,11 +3464,11 @@
       <c r="F27" s="28" t="inlineStr"/>
       <c r="G27" s="24">
         <f>IF(A27="","",MONTH(A27))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H27" s="24">
         <f>IF(A27="","",YEAR(A27))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="28">
@@ -3496,11 +3496,11 @@
       <c r="F28" s="28" t="inlineStr"/>
       <c r="G28" s="24">
         <f>IF(A28="","",MONTH(A28))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H28" s="24">
         <f>IF(A28="","",YEAR(A28))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="29">
@@ -3528,11 +3528,11 @@
       <c r="F29" s="28" t="inlineStr"/>
       <c r="G29" s="24">
         <f>IF(A29="","",MONTH(A29))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H29" s="24">
         <f>IF(A29="","",YEAR(A29))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="30">
@@ -3560,11 +3560,11 @@
       <c r="F30" s="28" t="inlineStr"/>
       <c r="G30" s="24">
         <f>IF(A30="","",MONTH(A30))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H30" s="24">
         <f>IF(A30="","",YEAR(A30))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="31">
@@ -3592,11 +3592,11 @@
       <c r="F31" s="28" t="inlineStr"/>
       <c r="G31" s="24">
         <f>IF(A31="","",MONTH(A31))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H31" s="24">
         <f>IF(A31="","",YEAR(A31))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="32">
@@ -3624,11 +3624,11 @@
       <c r="F32" s="28" t="inlineStr"/>
       <c r="G32" s="24">
         <f>IF(A32="","",MONTH(A32))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H32" s="24">
         <f>IF(A32="","",YEAR(A32))</f>
-        <v/>
+        <v>2026</v>
       </c>
     </row>
     <row r="33">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
@@ -726,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -887,17 +887,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -9599,7 +9611,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="B5:B404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$14,0,0,MAX(1,COUNTA(Config!$A$14:$A$19)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -9608,10 +9620,10 @@
     <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"1º trimestre,2º trimestre,3º trimestre,4º trimestre"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -226,16 +227,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,10 +244,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,21 +270,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -875,7 +876,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -899,7 +900,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1735,7 @@
         <v>10622</v>
       </c>
       <c r="F32" s="24" t="str">
-        <f>IF(Config!$B$7&gt;3,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$11&gt;=DATE(Config!$B$5,4,1),AND(COUNT('Resultado mensal'!B5:B7)&gt;=3,COUNT('Resultado mensal'!C5:C7)&gt;=3,COUNT('Resultado mensal'!D5:D7)&gt;=3)),"Sim","Em andamento")</f>
         <v>Sim</v>
       </c>
       <c r="G32" s="23">
@@ -1773,7 +1774,7 @@
         <v>15187</v>
       </c>
       <c r="F33" s="24" t="str">
-        <f>IF(Config!$B$7&gt;6,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$11&gt;=DATE(Config!$B$5,7,1),AND(COUNT('Resultado mensal'!B8:B10)&gt;=3,COUNT('Resultado mensal'!C8:C10)&gt;=3,COUNT('Resultado mensal'!D8:D10)&gt;=3)),"Sim","Em andamento")</f>
         <v>Sim</v>
       </c>
       <c r="G33" s="23">
@@ -1812,7 +1813,7 @@
         <v>1839</v>
       </c>
       <c r="F34" s="24" t="str">
-        <f>IF(Config!$B$7&gt;9,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$11&gt;=DATE(Config!$B$5,10,1),AND(COUNT('Resultado mensal'!B11:B13)&gt;=3,COUNT('Resultado mensal'!C11:C13)&gt;=3,COUNT('Resultado mensal'!D11:D13)&gt;=3)),"Sim","Em andamento")</f>
         <v>Em andamento</v>
       </c>
       <c r="G34" s="23">
@@ -1851,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="24" t="str">
-        <f>IF(Config!$B$7&gt;12,"Sim","Em andamento")</f>
+        <f>IF(AND(Config!$B$11&gt;=DATE(Config!$B$5+1,1,1),AND(COUNT('Resultado mensal'!B14:B16)&gt;=3,COUNT('Resultado mensal'!C14:C16)&gt;=3,COUNT('Resultado mensal'!D14:D16)&gt;=3)),"Sim","Em andamento")</f>
         <v>Em andamento</v>
       </c>
       <c r="G35" s="23">
@@ -1905,7 +1906,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:I35">
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>ROW()-32+1=Config!$B$8</formula>
+      <formula>ROW()-32+1=INDIRECT("Config!$B$8")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J14">
@@ -2110,7 +2111,7 @@
       </c>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>A distribuição é calculada só para trimestres já fechados (os três meses lançados em Resultado mensal e anteriores ao mês do painel).</t>
+          <t>A distribuição é calculada só para trimestres já fechados: o último dia do trimestre já passou (pela data de referência abaixo) E os três meses estão lançados em Resultado mensal, nas três colunas. Mês em branco não fecha o trimestre.</t>
         </is>
       </c>
       <c r="H10" s="29" t="inlineStr">
@@ -2119,7 +2120,20 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Data de referência (hoje)</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026. Ao usar com os seus dados, troque por =HOJE(). É esta data que decide se um trimestre já terminou.</t>
+        </is>
+      </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
           <t>Julho</t>
@@ -2222,20 +2236,20 @@
       <c r="C19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="35">
         <f>SUM(B14:B19)</f>
         <v>1</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>SUM(C14:C19)</f>
         <v>12000</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="37">
         <f>IF(ROUND(B20,4)=1,"","A participação deve somar 100 %")</f>
         <v/>
       </c>
@@ -2256,11 +2270,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="4">
-    <mergeCell ref="D10:F10"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D10:F10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -2346,11 +2361,11 @@
       <c r="C5" s="32" t="n">
         <v>8408</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="38">
         <f>IF(AND(B5="",C5=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="38">
         <f>B5-C5-D5</f>
         <v>642</v>
       </c>
@@ -2372,11 +2387,11 @@
       <c r="C6" s="32" t="n">
         <v>9204</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="38">
         <f>IF(AND(B6="",C6=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="38">
         <f>B6-C6-D6</f>
         <v>1866</v>
       </c>
@@ -2398,11 +2413,11 @@
       <c r="C7" s="32" t="n">
         <v>8476</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="38">
         <f>IF(AND(B7="",C7=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="38">
         <f>B7-C7-D7</f>
         <v>8114</v>
       </c>
@@ -2424,11 +2439,11 @@
       <c r="C8" s="32" t="n">
         <v>9327</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="38">
         <f>IF(AND(B8="",C8=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="38">
         <f>B8-C8-D8</f>
         <v>-1567</v>
       </c>
@@ -2450,11 +2465,11 @@
       <c r="C9" s="32" t="n">
         <v>8701</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="38">
         <f>IF(AND(B9="",C9=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="38">
         <f>B9-C9-D9</f>
         <v>10419</v>
       </c>
@@ -2476,11 +2491,11 @@
       <c r="C10" s="32" t="n">
         <v>9085</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="38">
         <f>IF(AND(B10="",C10=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="38">
         <f>B10-C10-D10</f>
         <v>6335</v>
       </c>
@@ -2502,11 +2517,11 @@
       <c r="C11" s="32" t="n">
         <v>9004</v>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="38">
         <f>IF(AND(B11="",C11=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="38">
         <f>B11-C11-D11</f>
         <v>8456</v>
       </c>
@@ -2528,11 +2543,11 @@
       <c r="C12" s="32" t="n">
         <v>9417</v>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="38">
         <f>IF(AND(B12="",C12=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="38">
         <f>B12-C12-D12</f>
         <v>5483</v>
       </c>
@@ -2554,11 +2569,11 @@
       <c r="C13" s="32" t="n">
         <v>5320</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="38">
         <f>IF(AND(B13="",C13=""),0,Config!$C$20)</f>
         <v>12000</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="38">
         <f>B13-C13-D13</f>
         <v>-12100</v>
       </c>
@@ -2576,11 +2591,11 @@
       </c>
       <c r="B14" s="32" t="n"/>
       <c r="C14" s="32" t="n"/>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>IF(AND(B14="",C14=""),0,Config!$C$20)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>B14-C14-D14</f>
         <v>0</v>
       </c>
@@ -2598,11 +2613,11 @@
       </c>
       <c r="B15" s="32" t="n"/>
       <c r="C15" s="32" t="n"/>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f>IF(AND(B15="",C15=""),0,Config!$C$20)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>B15-C15-D15</f>
         <v>0</v>
       </c>
@@ -2620,11 +2635,11 @@
       </c>
       <c r="B16" s="32" t="n"/>
       <c r="C16" s="32" t="n"/>
-      <c r="D16" s="37">
+      <c r="D16" s="38">
         <f>IF(AND(B16="",C16=""),0,Config!$C$20)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="38">
         <f>B16-C16-D16</f>
         <v>0</v>
       </c>
@@ -2732,7 +2747,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="n">
+      <c r="A5" s="33" t="n">
         <v>46050</v>
       </c>
       <c r="B5" s="28" t="inlineStr">
@@ -2764,7 +2779,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="33" t="n">
         <v>46050</v>
       </c>
       <c r="B6" s="28" t="inlineStr">
@@ -2796,7 +2811,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>46059</v>
       </c>
       <c r="B7" s="28" t="inlineStr">
@@ -2828,7 +2843,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>46081</v>
       </c>
       <c r="B8" s="28" t="inlineStr">
@@ -2860,7 +2875,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>46081</v>
       </c>
       <c r="B9" s="28" t="inlineStr">
@@ -2892,7 +2907,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>46092</v>
       </c>
       <c r="B10" s="28" t="inlineStr">
@@ -2924,7 +2939,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>46097</v>
       </c>
       <c r="B11" s="28" t="inlineStr">
@@ -2956,7 +2971,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>46109</v>
       </c>
       <c r="B12" s="28" t="inlineStr">
@@ -2988,7 +3003,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>46109</v>
       </c>
       <c r="B13" s="28" t="inlineStr">
@@ -3020,7 +3035,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="33" t="n">
         <v>46122</v>
       </c>
       <c r="B14" s="28" t="inlineStr">
@@ -3056,7 +3071,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="33" t="n">
         <v>46122</v>
       </c>
       <c r="B15" s="28" t="inlineStr">
@@ -3092,7 +3107,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="33" t="n">
         <v>46126</v>
       </c>
       <c r="B16" s="28" t="inlineStr">
@@ -3124,7 +3139,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="33" t="n">
         <v>46140</v>
       </c>
       <c r="B17" s="28" t="inlineStr">
@@ -3156,7 +3171,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n">
+      <c r="A18" s="33" t="n">
         <v>46140</v>
       </c>
       <c r="B18" s="28" t="inlineStr">
@@ -3188,7 +3203,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="33" t="n">
         <v>46148</v>
       </c>
       <c r="B19" s="28" t="inlineStr">
@@ -3220,7 +3235,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="n">
+      <c r="A20" s="33" t="n">
         <v>46170</v>
       </c>
       <c r="B20" s="28" t="inlineStr">
@@ -3252,7 +3267,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="n">
+      <c r="A21" s="33" t="n">
         <v>46170</v>
       </c>
       <c r="B21" s="28" t="inlineStr">
@@ -3284,7 +3299,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="33" t="n">
         <v>46192</v>
       </c>
       <c r="B22" s="28" t="inlineStr">
@@ -3316,7 +3331,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="33" t="n">
         <v>46201</v>
       </c>
       <c r="B23" s="28" t="inlineStr">
@@ -3348,7 +3363,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
+      <c r="A24" s="33" t="n">
         <v>46201</v>
       </c>
       <c r="B24" s="28" t="inlineStr">
@@ -3380,7 +3395,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
+      <c r="A25" s="33" t="n">
         <v>46213</v>
       </c>
       <c r="B25" s="28" t="inlineStr">
@@ -3416,7 +3431,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="n">
+      <c r="A26" s="33" t="n">
         <v>46213</v>
       </c>
       <c r="B26" s="28" t="inlineStr">
@@ -3452,7 +3467,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="n">
+      <c r="A27" s="33" t="n">
         <v>46214</v>
       </c>
       <c r="B27" s="28" t="inlineStr">
@@ -3484,7 +3499,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="n">
+      <c r="A28" s="33" t="n">
         <v>46231</v>
       </c>
       <c r="B28" s="28" t="inlineStr">
@@ -3516,7 +3531,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="n">
+      <c r="A29" s="33" t="n">
         <v>46231</v>
       </c>
       <c r="B29" s="28" t="inlineStr">
@@ -3548,7 +3563,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="n">
+      <c r="A30" s="33" t="n">
         <v>46240</v>
       </c>
       <c r="B30" s="28" t="inlineStr">
@@ -3580,7 +3595,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="n">
+      <c r="A31" s="33" t="n">
         <v>46262</v>
       </c>
       <c r="B31" s="28" t="inlineStr">
@@ -3612,7 +3627,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="n">
+      <c r="A32" s="33" t="n">
         <v>46262</v>
       </c>
       <c r="B32" s="28" t="inlineStr">
@@ -3644,7 +3659,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n"/>
+      <c r="A33" s="33" t="n"/>
       <c r="B33" s="28" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="27" t="n"/>
@@ -3660,7 +3675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="n"/>
+      <c r="A34" s="33" t="n"/>
       <c r="B34" s="28" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="27" t="n"/>
@@ -3676,7 +3691,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="38" t="n"/>
+      <c r="A35" s="33" t="n"/>
       <c r="B35" s="28" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="27" t="n"/>
@@ -3692,7 +3707,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="n"/>
+      <c r="A36" s="33" t="n"/>
       <c r="B36" s="28" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="27" t="n"/>
@@ -3708,7 +3723,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="n"/>
+      <c r="A37" s="33" t="n"/>
       <c r="B37" s="28" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="27" t="n"/>
@@ -3724,7 +3739,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="n"/>
+      <c r="A38" s="33" t="n"/>
       <c r="B38" s="28" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="27" t="n"/>
@@ -3740,7 +3755,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="n"/>
+      <c r="A39" s="33" t="n"/>
       <c r="B39" s="28" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="27" t="n"/>
@@ -3756,7 +3771,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="n"/>
+      <c r="A40" s="33" t="n"/>
       <c r="B40" s="28" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="27" t="n"/>
@@ -3772,7 +3787,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="n"/>
+      <c r="A41" s="33" t="n"/>
       <c r="B41" s="28" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="27" t="n"/>
@@ -3788,7 +3803,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="38" t="n"/>
+      <c r="A42" s="33" t="n"/>
       <c r="B42" s="28" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="27" t="n"/>
@@ -3804,7 +3819,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="38" t="n"/>
+      <c r="A43" s="33" t="n"/>
       <c r="B43" s="28" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="27" t="n"/>
@@ -3820,7 +3835,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="n"/>
+      <c r="A44" s="33" t="n"/>
       <c r="B44" s="28" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="27" t="n"/>
@@ -3836,7 +3851,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="n"/>
+      <c r="A45" s="33" t="n"/>
       <c r="B45" s="28" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="27" t="n"/>
@@ -3852,7 +3867,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38" t="n"/>
+      <c r="A46" s="33" t="n"/>
       <c r="B46" s="28" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="27" t="n"/>
@@ -3868,7 +3883,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38" t="n"/>
+      <c r="A47" s="33" t="n"/>
       <c r="B47" s="28" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="27" t="n"/>
@@ -3884,7 +3899,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="n"/>
+      <c r="A48" s="33" t="n"/>
       <c r="B48" s="28" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="27" t="n"/>
@@ -3900,7 +3915,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="n"/>
+      <c r="A49" s="33" t="n"/>
       <c r="B49" s="28" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="27" t="n"/>
@@ -3916,7 +3931,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="n"/>
+      <c r="A50" s="33" t="n"/>
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="27" t="n"/>
@@ -3932,7 +3947,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="38" t="n"/>
+      <c r="A51" s="33" t="n"/>
       <c r="B51" s="28" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="27" t="n"/>
@@ -3948,7 +3963,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="38" t="n"/>
+      <c r="A52" s="33" t="n"/>
       <c r="B52" s="28" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="27" t="n"/>
@@ -3964,7 +3979,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="38" t="n"/>
+      <c r="A53" s="33" t="n"/>
       <c r="B53" s="28" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="27" t="n"/>
@@ -3980,7 +3995,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="38" t="n"/>
+      <c r="A54" s="33" t="n"/>
       <c r="B54" s="28" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="27" t="n"/>
@@ -3996,7 +4011,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="38" t="n"/>
+      <c r="A55" s="33" t="n"/>
       <c r="B55" s="28" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="27" t="n"/>
@@ -4012,7 +4027,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="38" t="n"/>
+      <c r="A56" s="33" t="n"/>
       <c r="B56" s="28" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="27" t="n"/>
@@ -4028,7 +4043,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="38" t="n"/>
+      <c r="A57" s="33" t="n"/>
       <c r="B57" s="28" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="27" t="n"/>
@@ -4044,7 +4059,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="38" t="n"/>
+      <c r="A58" s="33" t="n"/>
       <c r="B58" s="28" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="27" t="n"/>
@@ -4060,7 +4075,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="38" t="n"/>
+      <c r="A59" s="33" t="n"/>
       <c r="B59" s="28" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="27" t="n"/>
@@ -4076,7 +4091,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="38" t="n"/>
+      <c r="A60" s="33" t="n"/>
       <c r="B60" s="28" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="27" t="n"/>
@@ -4092,7 +4107,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="38" t="n"/>
+      <c r="A61" s="33" t="n"/>
       <c r="B61" s="28" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="27" t="n"/>
@@ -4108,7 +4123,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="38" t="n"/>
+      <c r="A62" s="33" t="n"/>
       <c r="B62" s="28" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="27" t="n"/>
@@ -4124,7 +4139,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="38" t="n"/>
+      <c r="A63" s="33" t="n"/>
       <c r="B63" s="28" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="27" t="n"/>
@@ -4140,7 +4155,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="38" t="n"/>
+      <c r="A64" s="33" t="n"/>
       <c r="B64" s="28" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="27" t="n"/>
@@ -4156,7 +4171,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="38" t="n"/>
+      <c r="A65" s="33" t="n"/>
       <c r="B65" s="28" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="27" t="n"/>
@@ -4172,7 +4187,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="38" t="n"/>
+      <c r="A66" s="33" t="n"/>
       <c r="B66" s="28" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="27" t="n"/>
@@ -4188,7 +4203,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="38" t="n"/>
+      <c r="A67" s="33" t="n"/>
       <c r="B67" s="28" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="27" t="n"/>
@@ -4204,7 +4219,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="38" t="n"/>
+      <c r="A68" s="33" t="n"/>
       <c r="B68" s="28" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="27" t="n"/>
@@ -4220,7 +4235,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="38" t="n"/>
+      <c r="A69" s="33" t="n"/>
       <c r="B69" s="28" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="27" t="n"/>
@@ -4236,7 +4251,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="38" t="n"/>
+      <c r="A70" s="33" t="n"/>
       <c r="B70" s="28" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="27" t="n"/>
@@ -4252,7 +4267,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="38" t="n"/>
+      <c r="A71" s="33" t="n"/>
       <c r="B71" s="28" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="27" t="n"/>
@@ -4268,7 +4283,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="38" t="n"/>
+      <c r="A72" s="33" t="n"/>
       <c r="B72" s="28" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="27" t="n"/>
@@ -4284,7 +4299,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="38" t="n"/>
+      <c r="A73" s="33" t="n"/>
       <c r="B73" s="28" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="27" t="n"/>
@@ -4300,7 +4315,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="38" t="n"/>
+      <c r="A74" s="33" t="n"/>
       <c r="B74" s="28" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="27" t="n"/>
@@ -4316,7 +4331,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="38" t="n"/>
+      <c r="A75" s="33" t="n"/>
       <c r="B75" s="28" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="27" t="n"/>
@@ -4332,7 +4347,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="38" t="n"/>
+      <c r="A76" s="33" t="n"/>
       <c r="B76" s="28" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="27" t="n"/>
@@ -4348,7 +4363,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="38" t="n"/>
+      <c r="A77" s="33" t="n"/>
       <c r="B77" s="28" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="27" t="n"/>
@@ -4364,7 +4379,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="38" t="n"/>
+      <c r="A78" s="33" t="n"/>
       <c r="B78" s="28" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="27" t="n"/>
@@ -4380,7 +4395,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="38" t="n"/>
+      <c r="A79" s="33" t="n"/>
       <c r="B79" s="28" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="27" t="n"/>
@@ -4396,7 +4411,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="38" t="n"/>
+      <c r="A80" s="33" t="n"/>
       <c r="B80" s="28" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="27" t="n"/>
@@ -4412,7 +4427,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="38" t="n"/>
+      <c r="A81" s="33" t="n"/>
       <c r="B81" s="28" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="27" t="n"/>
@@ -4428,7 +4443,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="38" t="n"/>
+      <c r="A82" s="33" t="n"/>
       <c r="B82" s="28" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="27" t="n"/>
@@ -4444,7 +4459,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="38" t="n"/>
+      <c r="A83" s="33" t="n"/>
       <c r="B83" s="28" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="27" t="n"/>
@@ -4460,7 +4475,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="38" t="n"/>
+      <c r="A84" s="33" t="n"/>
       <c r="B84" s="28" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="27" t="n"/>
@@ -4476,7 +4491,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="38" t="n"/>
+      <c r="A85" s="33" t="n"/>
       <c r="B85" s="28" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="27" t="n"/>
@@ -4492,7 +4507,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="38" t="n"/>
+      <c r="A86" s="33" t="n"/>
       <c r="B86" s="28" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="27" t="n"/>
@@ -4508,7 +4523,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="38" t="n"/>
+      <c r="A87" s="33" t="n"/>
       <c r="B87" s="28" t="n"/>
       <c r="C87" s="28" t="n"/>
       <c r="D87" s="27" t="n"/>
@@ -4524,7 +4539,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="38" t="n"/>
+      <c r="A88" s="33" t="n"/>
       <c r="B88" s="28" t="n"/>
       <c r="C88" s="28" t="n"/>
       <c r="D88" s="27" t="n"/>
@@ -4540,7 +4555,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="38" t="n"/>
+      <c r="A89" s="33" t="n"/>
       <c r="B89" s="28" t="n"/>
       <c r="C89" s="28" t="n"/>
       <c r="D89" s="27" t="n"/>
@@ -4556,7 +4571,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="38" t="n"/>
+      <c r="A90" s="33" t="n"/>
       <c r="B90" s="28" t="n"/>
       <c r="C90" s="28" t="n"/>
       <c r="D90" s="27" t="n"/>
@@ -4572,7 +4587,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="38" t="n"/>
+      <c r="A91" s="33" t="n"/>
       <c r="B91" s="28" t="n"/>
       <c r="C91" s="28" t="n"/>
       <c r="D91" s="27" t="n"/>
@@ -4588,7 +4603,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="38" t="n"/>
+      <c r="A92" s="33" t="n"/>
       <c r="B92" s="28" t="n"/>
       <c r="C92" s="28" t="n"/>
       <c r="D92" s="27" t="n"/>
@@ -4604,7 +4619,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="38" t="n"/>
+      <c r="A93" s="33" t="n"/>
       <c r="B93" s="28" t="n"/>
       <c r="C93" s="28" t="n"/>
       <c r="D93" s="27" t="n"/>
@@ -4620,7 +4635,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="38" t="n"/>
+      <c r="A94" s="33" t="n"/>
       <c r="B94" s="28" t="n"/>
       <c r="C94" s="28" t="n"/>
       <c r="D94" s="27" t="n"/>
@@ -4636,7 +4651,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="38" t="n"/>
+      <c r="A95" s="33" t="n"/>
       <c r="B95" s="28" t="n"/>
       <c r="C95" s="28" t="n"/>
       <c r="D95" s="27" t="n"/>
@@ -4652,7 +4667,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="38" t="n"/>
+      <c r="A96" s="33" t="n"/>
       <c r="B96" s="28" t="n"/>
       <c r="C96" s="28" t="n"/>
       <c r="D96" s="27" t="n"/>
@@ -4668,7 +4683,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="38" t="n"/>
+      <c r="A97" s="33" t="n"/>
       <c r="B97" s="28" t="n"/>
       <c r="C97" s="28" t="n"/>
       <c r="D97" s="27" t="n"/>
@@ -4684,7 +4699,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="38" t="n"/>
+      <c r="A98" s="33" t="n"/>
       <c r="B98" s="28" t="n"/>
       <c r="C98" s="28" t="n"/>
       <c r="D98" s="27" t="n"/>
@@ -4700,7 +4715,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="38" t="n"/>
+      <c r="A99" s="33" t="n"/>
       <c r="B99" s="28" t="n"/>
       <c r="C99" s="28" t="n"/>
       <c r="D99" s="27" t="n"/>
@@ -4716,7 +4731,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="38" t="n"/>
+      <c r="A100" s="33" t="n"/>
       <c r="B100" s="28" t="n"/>
       <c r="C100" s="28" t="n"/>
       <c r="D100" s="27" t="n"/>
@@ -4732,7 +4747,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="38" t="n"/>
+      <c r="A101" s="33" t="n"/>
       <c r="B101" s="28" t="n"/>
       <c r="C101" s="28" t="n"/>
       <c r="D101" s="27" t="n"/>
@@ -4748,7 +4763,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="38" t="n"/>
+      <c r="A102" s="33" t="n"/>
       <c r="B102" s="28" t="n"/>
       <c r="C102" s="28" t="n"/>
       <c r="D102" s="27" t="n"/>
@@ -4764,7 +4779,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="38" t="n"/>
+      <c r="A103" s="33" t="n"/>
       <c r="B103" s="28" t="n"/>
       <c r="C103" s="28" t="n"/>
       <c r="D103" s="27" t="n"/>
@@ -4780,7 +4795,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="38" t="n"/>
+      <c r="A104" s="33" t="n"/>
       <c r="B104" s="28" t="n"/>
       <c r="C104" s="28" t="n"/>
       <c r="D104" s="27" t="n"/>
@@ -4796,7 +4811,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="38" t="n"/>
+      <c r="A105" s="33" t="n"/>
       <c r="B105" s="28" t="n"/>
       <c r="C105" s="28" t="n"/>
       <c r="D105" s="27" t="n"/>
@@ -4812,7 +4827,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="38" t="n"/>
+      <c r="A106" s="33" t="n"/>
       <c r="B106" s="28" t="n"/>
       <c r="C106" s="28" t="n"/>
       <c r="D106" s="27" t="n"/>
@@ -4828,7 +4843,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="38" t="n"/>
+      <c r="A107" s="33" t="n"/>
       <c r="B107" s="28" t="n"/>
       <c r="C107" s="28" t="n"/>
       <c r="D107" s="27" t="n"/>
@@ -4844,7 +4859,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="38" t="n"/>
+      <c r="A108" s="33" t="n"/>
       <c r="B108" s="28" t="n"/>
       <c r="C108" s="28" t="n"/>
       <c r="D108" s="27" t="n"/>
@@ -4860,7 +4875,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="38" t="n"/>
+      <c r="A109" s="33" t="n"/>
       <c r="B109" s="28" t="n"/>
       <c r="C109" s="28" t="n"/>
       <c r="D109" s="27" t="n"/>
@@ -4876,7 +4891,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="38" t="n"/>
+      <c r="A110" s="33" t="n"/>
       <c r="B110" s="28" t="n"/>
       <c r="C110" s="28" t="n"/>
       <c r="D110" s="27" t="n"/>
@@ -4892,7 +4907,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="38" t="n"/>
+      <c r="A111" s="33" t="n"/>
       <c r="B111" s="28" t="n"/>
       <c r="C111" s="28" t="n"/>
       <c r="D111" s="27" t="n"/>
@@ -4908,7 +4923,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="38" t="n"/>
+      <c r="A112" s="33" t="n"/>
       <c r="B112" s="28" t="n"/>
       <c r="C112" s="28" t="n"/>
       <c r="D112" s="27" t="n"/>
@@ -4924,7 +4939,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="38" t="n"/>
+      <c r="A113" s="33" t="n"/>
       <c r="B113" s="28" t="n"/>
       <c r="C113" s="28" t="n"/>
       <c r="D113" s="27" t="n"/>
@@ -4940,7 +4955,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="38" t="n"/>
+      <c r="A114" s="33" t="n"/>
       <c r="B114" s="28" t="n"/>
       <c r="C114" s="28" t="n"/>
       <c r="D114" s="27" t="n"/>
@@ -4956,7 +4971,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="38" t="n"/>
+      <c r="A115" s="33" t="n"/>
       <c r="B115" s="28" t="n"/>
       <c r="C115" s="28" t="n"/>
       <c r="D115" s="27" t="n"/>
@@ -4972,7 +4987,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="38" t="n"/>
+      <c r="A116" s="33" t="n"/>
       <c r="B116" s="28" t="n"/>
       <c r="C116" s="28" t="n"/>
       <c r="D116" s="27" t="n"/>
@@ -4988,7 +5003,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="38" t="n"/>
+      <c r="A117" s="33" t="n"/>
       <c r="B117" s="28" t="n"/>
       <c r="C117" s="28" t="n"/>
       <c r="D117" s="27" t="n"/>
@@ -5004,7 +5019,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="38" t="n"/>
+      <c r="A118" s="33" t="n"/>
       <c r="B118" s="28" t="n"/>
       <c r="C118" s="28" t="n"/>
       <c r="D118" s="27" t="n"/>
@@ -5020,7 +5035,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="38" t="n"/>
+      <c r="A119" s="33" t="n"/>
       <c r="B119" s="28" t="n"/>
       <c r="C119" s="28" t="n"/>
       <c r="D119" s="27" t="n"/>
@@ -5036,7 +5051,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="38" t="n"/>
+      <c r="A120" s="33" t="n"/>
       <c r="B120" s="28" t="n"/>
       <c r="C120" s="28" t="n"/>
       <c r="D120" s="27" t="n"/>
@@ -5052,7 +5067,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="38" t="n"/>
+      <c r="A121" s="33" t="n"/>
       <c r="B121" s="28" t="n"/>
       <c r="C121" s="28" t="n"/>
       <c r="D121" s="27" t="n"/>
@@ -5068,7 +5083,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="38" t="n"/>
+      <c r="A122" s="33" t="n"/>
       <c r="B122" s="28" t="n"/>
       <c r="C122" s="28" t="n"/>
       <c r="D122" s="27" t="n"/>
@@ -5084,7 +5099,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="38" t="n"/>
+      <c r="A123" s="33" t="n"/>
       <c r="B123" s="28" t="n"/>
       <c r="C123" s="28" t="n"/>
       <c r="D123" s="27" t="n"/>
@@ -5100,7 +5115,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="38" t="n"/>
+      <c r="A124" s="33" t="n"/>
       <c r="B124" s="28" t="n"/>
       <c r="C124" s="28" t="n"/>
       <c r="D124" s="27" t="n"/>
@@ -5116,7 +5131,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="38" t="n"/>
+      <c r="A125" s="33" t="n"/>
       <c r="B125" s="28" t="n"/>
       <c r="C125" s="28" t="n"/>
       <c r="D125" s="27" t="n"/>
@@ -5132,7 +5147,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="38" t="n"/>
+      <c r="A126" s="33" t="n"/>
       <c r="B126" s="28" t="n"/>
       <c r="C126" s="28" t="n"/>
       <c r="D126" s="27" t="n"/>
@@ -5148,7 +5163,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="38" t="n"/>
+      <c r="A127" s="33" t="n"/>
       <c r="B127" s="28" t="n"/>
       <c r="C127" s="28" t="n"/>
       <c r="D127" s="27" t="n"/>
@@ -5164,7 +5179,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="38" t="n"/>
+      <c r="A128" s="33" t="n"/>
       <c r="B128" s="28" t="n"/>
       <c r="C128" s="28" t="n"/>
       <c r="D128" s="27" t="n"/>
@@ -5180,7 +5195,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="38" t="n"/>
+      <c r="A129" s="33" t="n"/>
       <c r="B129" s="28" t="n"/>
       <c r="C129" s="28" t="n"/>
       <c r="D129" s="27" t="n"/>
@@ -5196,7 +5211,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="38" t="n"/>
+      <c r="A130" s="33" t="n"/>
       <c r="B130" s="28" t="n"/>
       <c r="C130" s="28" t="n"/>
       <c r="D130" s="27" t="n"/>
@@ -5212,7 +5227,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="38" t="n"/>
+      <c r="A131" s="33" t="n"/>
       <c r="B131" s="28" t="n"/>
       <c r="C131" s="28" t="n"/>
       <c r="D131" s="27" t="n"/>
@@ -5228,7 +5243,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="38" t="n"/>
+      <c r="A132" s="33" t="n"/>
       <c r="B132" s="28" t="n"/>
       <c r="C132" s="28" t="n"/>
       <c r="D132" s="27" t="n"/>
@@ -5244,7 +5259,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="38" t="n"/>
+      <c r="A133" s="33" t="n"/>
       <c r="B133" s="28" t="n"/>
       <c r="C133" s="28" t="n"/>
       <c r="D133" s="27" t="n"/>
@@ -5260,7 +5275,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="38" t="n"/>
+      <c r="A134" s="33" t="n"/>
       <c r="B134" s="28" t="n"/>
       <c r="C134" s="28" t="n"/>
       <c r="D134" s="27" t="n"/>
@@ -5276,7 +5291,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="38" t="n"/>
+      <c r="A135" s="33" t="n"/>
       <c r="B135" s="28" t="n"/>
       <c r="C135" s="28" t="n"/>
       <c r="D135" s="27" t="n"/>
@@ -5292,7 +5307,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="38" t="n"/>
+      <c r="A136" s="33" t="n"/>
       <c r="B136" s="28" t="n"/>
       <c r="C136" s="28" t="n"/>
       <c r="D136" s="27" t="n"/>
@@ -5308,7 +5323,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="38" t="n"/>
+      <c r="A137" s="33" t="n"/>
       <c r="B137" s="28" t="n"/>
       <c r="C137" s="28" t="n"/>
       <c r="D137" s="27" t="n"/>
@@ -5324,7 +5339,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="38" t="n"/>
+      <c r="A138" s="33" t="n"/>
       <c r="B138" s="28" t="n"/>
       <c r="C138" s="28" t="n"/>
       <c r="D138" s="27" t="n"/>
@@ -5340,7 +5355,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="38" t="n"/>
+      <c r="A139" s="33" t="n"/>
       <c r="B139" s="28" t="n"/>
       <c r="C139" s="28" t="n"/>
       <c r="D139" s="27" t="n"/>
@@ -5356,7 +5371,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="38" t="n"/>
+      <c r="A140" s="33" t="n"/>
       <c r="B140" s="28" t="n"/>
       <c r="C140" s="28" t="n"/>
       <c r="D140" s="27" t="n"/>
@@ -5372,7 +5387,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="38" t="n"/>
+      <c r="A141" s="33" t="n"/>
       <c r="B141" s="28" t="n"/>
       <c r="C141" s="28" t="n"/>
       <c r="D141" s="27" t="n"/>
@@ -5388,7 +5403,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="38" t="n"/>
+      <c r="A142" s="33" t="n"/>
       <c r="B142" s="28" t="n"/>
       <c r="C142" s="28" t="n"/>
       <c r="D142" s="27" t="n"/>
@@ -5404,7 +5419,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="38" t="n"/>
+      <c r="A143" s="33" t="n"/>
       <c r="B143" s="28" t="n"/>
       <c r="C143" s="28" t="n"/>
       <c r="D143" s="27" t="n"/>
@@ -5420,7 +5435,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="38" t="n"/>
+      <c r="A144" s="33" t="n"/>
       <c r="B144" s="28" t="n"/>
       <c r="C144" s="28" t="n"/>
       <c r="D144" s="27" t="n"/>
@@ -5436,7 +5451,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="38" t="n"/>
+      <c r="A145" s="33" t="n"/>
       <c r="B145" s="28" t="n"/>
       <c r="C145" s="28" t="n"/>
       <c r="D145" s="27" t="n"/>
@@ -5452,7 +5467,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="38" t="n"/>
+      <c r="A146" s="33" t="n"/>
       <c r="B146" s="28" t="n"/>
       <c r="C146" s="28" t="n"/>
       <c r="D146" s="27" t="n"/>
@@ -5468,7 +5483,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="38" t="n"/>
+      <c r="A147" s="33" t="n"/>
       <c r="B147" s="28" t="n"/>
       <c r="C147" s="28" t="n"/>
       <c r="D147" s="27" t="n"/>
@@ -5484,7 +5499,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="38" t="n"/>
+      <c r="A148" s="33" t="n"/>
       <c r="B148" s="28" t="n"/>
       <c r="C148" s="28" t="n"/>
       <c r="D148" s="27" t="n"/>
@@ -5500,7 +5515,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="38" t="n"/>
+      <c r="A149" s="33" t="n"/>
       <c r="B149" s="28" t="n"/>
       <c r="C149" s="28" t="n"/>
       <c r="D149" s="27" t="n"/>
@@ -5516,7 +5531,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="38" t="n"/>
+      <c r="A150" s="33" t="n"/>
       <c r="B150" s="28" t="n"/>
       <c r="C150" s="28" t="n"/>
       <c r="D150" s="27" t="n"/>
@@ -5532,7 +5547,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="38" t="n"/>
+      <c r="A151" s="33" t="n"/>
       <c r="B151" s="28" t="n"/>
       <c r="C151" s="28" t="n"/>
       <c r="D151" s="27" t="n"/>
@@ -5548,7 +5563,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="38" t="n"/>
+      <c r="A152" s="33" t="n"/>
       <c r="B152" s="28" t="n"/>
       <c r="C152" s="28" t="n"/>
       <c r="D152" s="27" t="n"/>
@@ -5564,7 +5579,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="38" t="n"/>
+      <c r="A153" s="33" t="n"/>
       <c r="B153" s="28" t="n"/>
       <c r="C153" s="28" t="n"/>
       <c r="D153" s="27" t="n"/>
@@ -5580,7 +5595,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="38" t="n"/>
+      <c r="A154" s="33" t="n"/>
       <c r="B154" s="28" t="n"/>
       <c r="C154" s="28" t="n"/>
       <c r="D154" s="27" t="n"/>
@@ -5596,7 +5611,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="38" t="n"/>
+      <c r="A155" s="33" t="n"/>
       <c r="B155" s="28" t="n"/>
       <c r="C155" s="28" t="n"/>
       <c r="D155" s="27" t="n"/>
@@ -5612,7 +5627,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="38" t="n"/>
+      <c r="A156" s="33" t="n"/>
       <c r="B156" s="28" t="n"/>
       <c r="C156" s="28" t="n"/>
       <c r="D156" s="27" t="n"/>
@@ -5628,7 +5643,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="38" t="n"/>
+      <c r="A157" s="33" t="n"/>
       <c r="B157" s="28" t="n"/>
       <c r="C157" s="28" t="n"/>
       <c r="D157" s="27" t="n"/>
@@ -5644,7 +5659,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="38" t="n"/>
+      <c r="A158" s="33" t="n"/>
       <c r="B158" s="28" t="n"/>
       <c r="C158" s="28" t="n"/>
       <c r="D158" s="27" t="n"/>
@@ -5660,7 +5675,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="38" t="n"/>
+      <c r="A159" s="33" t="n"/>
       <c r="B159" s="28" t="n"/>
       <c r="C159" s="28" t="n"/>
       <c r="D159" s="27" t="n"/>
@@ -5676,7 +5691,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="38" t="n"/>
+      <c r="A160" s="33" t="n"/>
       <c r="B160" s="28" t="n"/>
       <c r="C160" s="28" t="n"/>
       <c r="D160" s="27" t="n"/>
@@ -5692,7 +5707,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="38" t="n"/>
+      <c r="A161" s="33" t="n"/>
       <c r="B161" s="28" t="n"/>
       <c r="C161" s="28" t="n"/>
       <c r="D161" s="27" t="n"/>
@@ -5708,7 +5723,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="38" t="n"/>
+      <c r="A162" s="33" t="n"/>
       <c r="B162" s="28" t="n"/>
       <c r="C162" s="28" t="n"/>
       <c r="D162" s="27" t="n"/>
@@ -5724,7 +5739,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="38" t="n"/>
+      <c r="A163" s="33" t="n"/>
       <c r="B163" s="28" t="n"/>
       <c r="C163" s="28" t="n"/>
       <c r="D163" s="27" t="n"/>
@@ -5740,7 +5755,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="38" t="n"/>
+      <c r="A164" s="33" t="n"/>
       <c r="B164" s="28" t="n"/>
       <c r="C164" s="28" t="n"/>
       <c r="D164" s="27" t="n"/>
@@ -5756,7 +5771,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="38" t="n"/>
+      <c r="A165" s="33" t="n"/>
       <c r="B165" s="28" t="n"/>
       <c r="C165" s="28" t="n"/>
       <c r="D165" s="27" t="n"/>
@@ -5772,7 +5787,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="38" t="n"/>
+      <c r="A166" s="33" t="n"/>
       <c r="B166" s="28" t="n"/>
       <c r="C166" s="28" t="n"/>
       <c r="D166" s="27" t="n"/>
@@ -5788,7 +5803,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="38" t="n"/>
+      <c r="A167" s="33" t="n"/>
       <c r="B167" s="28" t="n"/>
       <c r="C167" s="28" t="n"/>
       <c r="D167" s="27" t="n"/>
@@ -5804,7 +5819,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="38" t="n"/>
+      <c r="A168" s="33" t="n"/>
       <c r="B168" s="28" t="n"/>
       <c r="C168" s="28" t="n"/>
       <c r="D168" s="27" t="n"/>
@@ -5820,7 +5835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="38" t="n"/>
+      <c r="A169" s="33" t="n"/>
       <c r="B169" s="28" t="n"/>
       <c r="C169" s="28" t="n"/>
       <c r="D169" s="27" t="n"/>
@@ -5836,7 +5851,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="38" t="n"/>
+      <c r="A170" s="33" t="n"/>
       <c r="B170" s="28" t="n"/>
       <c r="C170" s="28" t="n"/>
       <c r="D170" s="27" t="n"/>
@@ -5852,7 +5867,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="38" t="n"/>
+      <c r="A171" s="33" t="n"/>
       <c r="B171" s="28" t="n"/>
       <c r="C171" s="28" t="n"/>
       <c r="D171" s="27" t="n"/>
@@ -5868,7 +5883,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="38" t="n"/>
+      <c r="A172" s="33" t="n"/>
       <c r="B172" s="28" t="n"/>
       <c r="C172" s="28" t="n"/>
       <c r="D172" s="27" t="n"/>
@@ -5884,7 +5899,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="38" t="n"/>
+      <c r="A173" s="33" t="n"/>
       <c r="B173" s="28" t="n"/>
       <c r="C173" s="28" t="n"/>
       <c r="D173" s="27" t="n"/>
@@ -5900,7 +5915,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="38" t="n"/>
+      <c r="A174" s="33" t="n"/>
       <c r="B174" s="28" t="n"/>
       <c r="C174" s="28" t="n"/>
       <c r="D174" s="27" t="n"/>
@@ -5916,7 +5931,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="38" t="n"/>
+      <c r="A175" s="33" t="n"/>
       <c r="B175" s="28" t="n"/>
       <c r="C175" s="28" t="n"/>
       <c r="D175" s="27" t="n"/>
@@ -5932,7 +5947,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="38" t="n"/>
+      <c r="A176" s="33" t="n"/>
       <c r="B176" s="28" t="n"/>
       <c r="C176" s="28" t="n"/>
       <c r="D176" s="27" t="n"/>
@@ -5948,7 +5963,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="38" t="n"/>
+      <c r="A177" s="33" t="n"/>
       <c r="B177" s="28" t="n"/>
       <c r="C177" s="28" t="n"/>
       <c r="D177" s="27" t="n"/>
@@ -5964,7 +5979,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="38" t="n"/>
+      <c r="A178" s="33" t="n"/>
       <c r="B178" s="28" t="n"/>
       <c r="C178" s="28" t="n"/>
       <c r="D178" s="27" t="n"/>
@@ -5980,7 +5995,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="38" t="n"/>
+      <c r="A179" s="33" t="n"/>
       <c r="B179" s="28" t="n"/>
       <c r="C179" s="28" t="n"/>
       <c r="D179" s="27" t="n"/>
@@ -5996,7 +6011,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="38" t="n"/>
+      <c r="A180" s="33" t="n"/>
       <c r="B180" s="28" t="n"/>
       <c r="C180" s="28" t="n"/>
       <c r="D180" s="27" t="n"/>
@@ -6012,7 +6027,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="38" t="n"/>
+      <c r="A181" s="33" t="n"/>
       <c r="B181" s="28" t="n"/>
       <c r="C181" s="28" t="n"/>
       <c r="D181" s="27" t="n"/>
@@ -6028,7 +6043,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="38" t="n"/>
+      <c r="A182" s="33" t="n"/>
       <c r="B182" s="28" t="n"/>
       <c r="C182" s="28" t="n"/>
       <c r="D182" s="27" t="n"/>
@@ -6044,7 +6059,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="38" t="n"/>
+      <c r="A183" s="33" t="n"/>
       <c r="B183" s="28" t="n"/>
       <c r="C183" s="28" t="n"/>
       <c r="D183" s="27" t="n"/>
@@ -6060,7 +6075,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="38" t="n"/>
+      <c r="A184" s="33" t="n"/>
       <c r="B184" s="28" t="n"/>
       <c r="C184" s="28" t="n"/>
       <c r="D184" s="27" t="n"/>
@@ -6076,7 +6091,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="38" t="n"/>
+      <c r="A185" s="33" t="n"/>
       <c r="B185" s="28" t="n"/>
       <c r="C185" s="28" t="n"/>
       <c r="D185" s="27" t="n"/>
@@ -6092,7 +6107,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="38" t="n"/>
+      <c r="A186" s="33" t="n"/>
       <c r="B186" s="28" t="n"/>
       <c r="C186" s="28" t="n"/>
       <c r="D186" s="27" t="n"/>
@@ -6108,7 +6123,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="38" t="n"/>
+      <c r="A187" s="33" t="n"/>
       <c r="B187" s="28" t="n"/>
       <c r="C187" s="28" t="n"/>
       <c r="D187" s="27" t="n"/>
@@ -6124,7 +6139,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="38" t="n"/>
+      <c r="A188" s="33" t="n"/>
       <c r="B188" s="28" t="n"/>
       <c r="C188" s="28" t="n"/>
       <c r="D188" s="27" t="n"/>
@@ -6140,7 +6155,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="38" t="n"/>
+      <c r="A189" s="33" t="n"/>
       <c r="B189" s="28" t="n"/>
       <c r="C189" s="28" t="n"/>
       <c r="D189" s="27" t="n"/>
@@ -6156,7 +6171,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="38" t="n"/>
+      <c r="A190" s="33" t="n"/>
       <c r="B190" s="28" t="n"/>
       <c r="C190" s="28" t="n"/>
       <c r="D190" s="27" t="n"/>
@@ -6172,7 +6187,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="38" t="n"/>
+      <c r="A191" s="33" t="n"/>
       <c r="B191" s="28" t="n"/>
       <c r="C191" s="28" t="n"/>
       <c r="D191" s="27" t="n"/>
@@ -6188,7 +6203,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="38" t="n"/>
+      <c r="A192" s="33" t="n"/>
       <c r="B192" s="28" t="n"/>
       <c r="C192" s="28" t="n"/>
       <c r="D192" s="27" t="n"/>
@@ -6204,7 +6219,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="38" t="n"/>
+      <c r="A193" s="33" t="n"/>
       <c r="B193" s="28" t="n"/>
       <c r="C193" s="28" t="n"/>
       <c r="D193" s="27" t="n"/>
@@ -6220,7 +6235,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="38" t="n"/>
+      <c r="A194" s="33" t="n"/>
       <c r="B194" s="28" t="n"/>
       <c r="C194" s="28" t="n"/>
       <c r="D194" s="27" t="n"/>
@@ -6236,7 +6251,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="38" t="n"/>
+      <c r="A195" s="33" t="n"/>
       <c r="B195" s="28" t="n"/>
       <c r="C195" s="28" t="n"/>
       <c r="D195" s="27" t="n"/>
@@ -6252,7 +6267,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="38" t="n"/>
+      <c r="A196" s="33" t="n"/>
       <c r="B196" s="28" t="n"/>
       <c r="C196" s="28" t="n"/>
       <c r="D196" s="27" t="n"/>
@@ -6268,7 +6283,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="38" t="n"/>
+      <c r="A197" s="33" t="n"/>
       <c r="B197" s="28" t="n"/>
       <c r="C197" s="28" t="n"/>
       <c r="D197" s="27" t="n"/>
@@ -6284,7 +6299,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="38" t="n"/>
+      <c r="A198" s="33" t="n"/>
       <c r="B198" s="28" t="n"/>
       <c r="C198" s="28" t="n"/>
       <c r="D198" s="27" t="n"/>
@@ -6300,7 +6315,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="38" t="n"/>
+      <c r="A199" s="33" t="n"/>
       <c r="B199" s="28" t="n"/>
       <c r="C199" s="28" t="n"/>
       <c r="D199" s="27" t="n"/>
@@ -6316,7 +6331,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="38" t="n"/>
+      <c r="A200" s="33" t="n"/>
       <c r="B200" s="28" t="n"/>
       <c r="C200" s="28" t="n"/>
       <c r="D200" s="27" t="n"/>
@@ -6332,7 +6347,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="38" t="n"/>
+      <c r="A201" s="33" t="n"/>
       <c r="B201" s="28" t="n"/>
       <c r="C201" s="28" t="n"/>
       <c r="D201" s="27" t="n"/>
@@ -6348,7 +6363,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="38" t="n"/>
+      <c r="A202" s="33" t="n"/>
       <c r="B202" s="28" t="n"/>
       <c r="C202" s="28" t="n"/>
       <c r="D202" s="27" t="n"/>
@@ -6364,7 +6379,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="38" t="n"/>
+      <c r="A203" s="33" t="n"/>
       <c r="B203" s="28" t="n"/>
       <c r="C203" s="28" t="n"/>
       <c r="D203" s="27" t="n"/>
@@ -6380,7 +6395,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="38" t="n"/>
+      <c r="A204" s="33" t="n"/>
       <c r="B204" s="28" t="n"/>
       <c r="C204" s="28" t="n"/>
       <c r="D204" s="27" t="n"/>
@@ -6396,7 +6411,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="38" t="n"/>
+      <c r="A205" s="33" t="n"/>
       <c r="B205" s="28" t="n"/>
       <c r="C205" s="28" t="n"/>
       <c r="D205" s="27" t="n"/>
@@ -6412,7 +6427,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="38" t="n"/>
+      <c r="A206" s="33" t="n"/>
       <c r="B206" s="28" t="n"/>
       <c r="C206" s="28" t="n"/>
       <c r="D206" s="27" t="n"/>
@@ -6428,7 +6443,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="38" t="n"/>
+      <c r="A207" s="33" t="n"/>
       <c r="B207" s="28" t="n"/>
       <c r="C207" s="28" t="n"/>
       <c r="D207" s="27" t="n"/>
@@ -6444,7 +6459,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="38" t="n"/>
+      <c r="A208" s="33" t="n"/>
       <c r="B208" s="28" t="n"/>
       <c r="C208" s="28" t="n"/>
       <c r="D208" s="27" t="n"/>
@@ -6460,7 +6475,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="38" t="n"/>
+      <c r="A209" s="33" t="n"/>
       <c r="B209" s="28" t="n"/>
       <c r="C209" s="28" t="n"/>
       <c r="D209" s="27" t="n"/>
@@ -6476,7 +6491,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="38" t="n"/>
+      <c r="A210" s="33" t="n"/>
       <c r="B210" s="28" t="n"/>
       <c r="C210" s="28" t="n"/>
       <c r="D210" s="27" t="n"/>
@@ -6492,7 +6507,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="38" t="n"/>
+      <c r="A211" s="33" t="n"/>
       <c r="B211" s="28" t="n"/>
       <c r="C211" s="28" t="n"/>
       <c r="D211" s="27" t="n"/>
@@ -6508,7 +6523,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="38" t="n"/>
+      <c r="A212" s="33" t="n"/>
       <c r="B212" s="28" t="n"/>
       <c r="C212" s="28" t="n"/>
       <c r="D212" s="27" t="n"/>
@@ -6524,7 +6539,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="38" t="n"/>
+      <c r="A213" s="33" t="n"/>
       <c r="B213" s="28" t="n"/>
       <c r="C213" s="28" t="n"/>
       <c r="D213" s="27" t="n"/>
@@ -6540,7 +6555,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="38" t="n"/>
+      <c r="A214" s="33" t="n"/>
       <c r="B214" s="28" t="n"/>
       <c r="C214" s="28" t="n"/>
       <c r="D214" s="27" t="n"/>
@@ -6556,7 +6571,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="38" t="n"/>
+      <c r="A215" s="33" t="n"/>
       <c r="B215" s="28" t="n"/>
       <c r="C215" s="28" t="n"/>
       <c r="D215" s="27" t="n"/>
@@ -6572,7 +6587,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="38" t="n"/>
+      <c r="A216" s="33" t="n"/>
       <c r="B216" s="28" t="n"/>
       <c r="C216" s="28" t="n"/>
       <c r="D216" s="27" t="n"/>
@@ -6588,7 +6603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="38" t="n"/>
+      <c r="A217" s="33" t="n"/>
       <c r="B217" s="28" t="n"/>
       <c r="C217" s="28" t="n"/>
       <c r="D217" s="27" t="n"/>
@@ -6604,7 +6619,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="38" t="n"/>
+      <c r="A218" s="33" t="n"/>
       <c r="B218" s="28" t="n"/>
       <c r="C218" s="28" t="n"/>
       <c r="D218" s="27" t="n"/>
@@ -6620,7 +6635,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="38" t="n"/>
+      <c r="A219" s="33" t="n"/>
       <c r="B219" s="28" t="n"/>
       <c r="C219" s="28" t="n"/>
       <c r="D219" s="27" t="n"/>
@@ -6636,7 +6651,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="38" t="n"/>
+      <c r="A220" s="33" t="n"/>
       <c r="B220" s="28" t="n"/>
       <c r="C220" s="28" t="n"/>
       <c r="D220" s="27" t="n"/>
@@ -6652,7 +6667,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="38" t="n"/>
+      <c r="A221" s="33" t="n"/>
       <c r="B221" s="28" t="n"/>
       <c r="C221" s="28" t="n"/>
       <c r="D221" s="27" t="n"/>
@@ -6668,7 +6683,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="38" t="n"/>
+      <c r="A222" s="33" t="n"/>
       <c r="B222" s="28" t="n"/>
       <c r="C222" s="28" t="n"/>
       <c r="D222" s="27" t="n"/>
@@ -6684,7 +6699,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="38" t="n"/>
+      <c r="A223" s="33" t="n"/>
       <c r="B223" s="28" t="n"/>
       <c r="C223" s="28" t="n"/>
       <c r="D223" s="27" t="n"/>
@@ -6700,7 +6715,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="38" t="n"/>
+      <c r="A224" s="33" t="n"/>
       <c r="B224" s="28" t="n"/>
       <c r="C224" s="28" t="n"/>
       <c r="D224" s="27" t="n"/>
@@ -6716,7 +6731,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="38" t="n"/>
+      <c r="A225" s="33" t="n"/>
       <c r="B225" s="28" t="n"/>
       <c r="C225" s="28" t="n"/>
       <c r="D225" s="27" t="n"/>
@@ -6732,7 +6747,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="38" t="n"/>
+      <c r="A226" s="33" t="n"/>
       <c r="B226" s="28" t="n"/>
       <c r="C226" s="28" t="n"/>
       <c r="D226" s="27" t="n"/>
@@ -6748,7 +6763,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="38" t="n"/>
+      <c r="A227" s="33" t="n"/>
       <c r="B227" s="28" t="n"/>
       <c r="C227" s="28" t="n"/>
       <c r="D227" s="27" t="n"/>
@@ -6764,7 +6779,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="38" t="n"/>
+      <c r="A228" s="33" t="n"/>
       <c r="B228" s="28" t="n"/>
       <c r="C228" s="28" t="n"/>
       <c r="D228" s="27" t="n"/>
@@ -6780,7 +6795,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="38" t="n"/>
+      <c r="A229" s="33" t="n"/>
       <c r="B229" s="28" t="n"/>
       <c r="C229" s="28" t="n"/>
       <c r="D229" s="27" t="n"/>
@@ -6796,7 +6811,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="38" t="n"/>
+      <c r="A230" s="33" t="n"/>
       <c r="B230" s="28" t="n"/>
       <c r="C230" s="28" t="n"/>
       <c r="D230" s="27" t="n"/>
@@ -6812,7 +6827,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="38" t="n"/>
+      <c r="A231" s="33" t="n"/>
       <c r="B231" s="28" t="n"/>
       <c r="C231" s="28" t="n"/>
       <c r="D231" s="27" t="n"/>
@@ -6828,7 +6843,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="38" t="n"/>
+      <c r="A232" s="33" t="n"/>
       <c r="B232" s="28" t="n"/>
       <c r="C232" s="28" t="n"/>
       <c r="D232" s="27" t="n"/>
@@ -6844,7 +6859,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="38" t="n"/>
+      <c r="A233" s="33" t="n"/>
       <c r="B233" s="28" t="n"/>
       <c r="C233" s="28" t="n"/>
       <c r="D233" s="27" t="n"/>
@@ -6860,7 +6875,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="38" t="n"/>
+      <c r="A234" s="33" t="n"/>
       <c r="B234" s="28" t="n"/>
       <c r="C234" s="28" t="n"/>
       <c r="D234" s="27" t="n"/>
@@ -6876,7 +6891,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="38" t="n"/>
+      <c r="A235" s="33" t="n"/>
       <c r="B235" s="28" t="n"/>
       <c r="C235" s="28" t="n"/>
       <c r="D235" s="27" t="n"/>
@@ -6892,7 +6907,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="38" t="n"/>
+      <c r="A236" s="33" t="n"/>
       <c r="B236" s="28" t="n"/>
       <c r="C236" s="28" t="n"/>
       <c r="D236" s="27" t="n"/>
@@ -6908,7 +6923,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="38" t="n"/>
+      <c r="A237" s="33" t="n"/>
       <c r="B237" s="28" t="n"/>
       <c r="C237" s="28" t="n"/>
       <c r="D237" s="27" t="n"/>
@@ -6924,7 +6939,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="38" t="n"/>
+      <c r="A238" s="33" t="n"/>
       <c r="B238" s="28" t="n"/>
       <c r="C238" s="28" t="n"/>
       <c r="D238" s="27" t="n"/>
@@ -6940,7 +6955,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="38" t="n"/>
+      <c r="A239" s="33" t="n"/>
       <c r="B239" s="28" t="n"/>
       <c r="C239" s="28" t="n"/>
       <c r="D239" s="27" t="n"/>
@@ -6956,7 +6971,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="38" t="n"/>
+      <c r="A240" s="33" t="n"/>
       <c r="B240" s="28" t="n"/>
       <c r="C240" s="28" t="n"/>
       <c r="D240" s="27" t="n"/>
@@ -6972,7 +6987,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="38" t="n"/>
+      <c r="A241" s="33" t="n"/>
       <c r="B241" s="28" t="n"/>
       <c r="C241" s="28" t="n"/>
       <c r="D241" s="27" t="n"/>
@@ -6988,7 +7003,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="38" t="n"/>
+      <c r="A242" s="33" t="n"/>
       <c r="B242" s="28" t="n"/>
       <c r="C242" s="28" t="n"/>
       <c r="D242" s="27" t="n"/>
@@ -7004,7 +7019,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="38" t="n"/>
+      <c r="A243" s="33" t="n"/>
       <c r="B243" s="28" t="n"/>
       <c r="C243" s="28" t="n"/>
       <c r="D243" s="27" t="n"/>
@@ -7020,7 +7035,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="38" t="n"/>
+      <c r="A244" s="33" t="n"/>
       <c r="B244" s="28" t="n"/>
       <c r="C244" s="28" t="n"/>
       <c r="D244" s="27" t="n"/>
@@ -7036,7 +7051,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="38" t="n"/>
+      <c r="A245" s="33" t="n"/>
       <c r="B245" s="28" t="n"/>
       <c r="C245" s="28" t="n"/>
       <c r="D245" s="27" t="n"/>
@@ -7052,7 +7067,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="38" t="n"/>
+      <c r="A246" s="33" t="n"/>
       <c r="B246" s="28" t="n"/>
       <c r="C246" s="28" t="n"/>
       <c r="D246" s="27" t="n"/>
@@ -7068,7 +7083,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="38" t="n"/>
+      <c r="A247" s="33" t="n"/>
       <c r="B247" s="28" t="n"/>
       <c r="C247" s="28" t="n"/>
       <c r="D247" s="27" t="n"/>
@@ -7084,7 +7099,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="38" t="n"/>
+      <c r="A248" s="33" t="n"/>
       <c r="B248" s="28" t="n"/>
       <c r="C248" s="28" t="n"/>
       <c r="D248" s="27" t="n"/>
@@ -7100,7 +7115,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="38" t="n"/>
+      <c r="A249" s="33" t="n"/>
       <c r="B249" s="28" t="n"/>
       <c r="C249" s="28" t="n"/>
       <c r="D249" s="27" t="n"/>
@@ -7116,7 +7131,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="38" t="n"/>
+      <c r="A250" s="33" t="n"/>
       <c r="B250" s="28" t="n"/>
       <c r="C250" s="28" t="n"/>
       <c r="D250" s="27" t="n"/>
@@ -7132,7 +7147,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="38" t="n"/>
+      <c r="A251" s="33" t="n"/>
       <c r="B251" s="28" t="n"/>
       <c r="C251" s="28" t="n"/>
       <c r="D251" s="27" t="n"/>
@@ -7148,7 +7163,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="38" t="n"/>
+      <c r="A252" s="33" t="n"/>
       <c r="B252" s="28" t="n"/>
       <c r="C252" s="28" t="n"/>
       <c r="D252" s="27" t="n"/>
@@ -7164,7 +7179,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="38" t="n"/>
+      <c r="A253" s="33" t="n"/>
       <c r="B253" s="28" t="n"/>
       <c r="C253" s="28" t="n"/>
       <c r="D253" s="27" t="n"/>
@@ -7180,7 +7195,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="38" t="n"/>
+      <c r="A254" s="33" t="n"/>
       <c r="B254" s="28" t="n"/>
       <c r="C254" s="28" t="n"/>
       <c r="D254" s="27" t="n"/>
@@ -7196,7 +7211,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="38" t="n"/>
+      <c r="A255" s="33" t="n"/>
       <c r="B255" s="28" t="n"/>
       <c r="C255" s="28" t="n"/>
       <c r="D255" s="27" t="n"/>
@@ -7212,7 +7227,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="38" t="n"/>
+      <c r="A256" s="33" t="n"/>
       <c r="B256" s="28" t="n"/>
       <c r="C256" s="28" t="n"/>
       <c r="D256" s="27" t="n"/>
@@ -7228,7 +7243,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="38" t="n"/>
+      <c r="A257" s="33" t="n"/>
       <c r="B257" s="28" t="n"/>
       <c r="C257" s="28" t="n"/>
       <c r="D257" s="27" t="n"/>
@@ -7244,7 +7259,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="38" t="n"/>
+      <c r="A258" s="33" t="n"/>
       <c r="B258" s="28" t="n"/>
       <c r="C258" s="28" t="n"/>
       <c r="D258" s="27" t="n"/>
@@ -7260,7 +7275,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="38" t="n"/>
+      <c r="A259" s="33" t="n"/>
       <c r="B259" s="28" t="n"/>
       <c r="C259" s="28" t="n"/>
       <c r="D259" s="27" t="n"/>
@@ -7276,7 +7291,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="38" t="n"/>
+      <c r="A260" s="33" t="n"/>
       <c r="B260" s="28" t="n"/>
       <c r="C260" s="28" t="n"/>
       <c r="D260" s="27" t="n"/>
@@ -7292,7 +7307,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="38" t="n"/>
+      <c r="A261" s="33" t="n"/>
       <c r="B261" s="28" t="n"/>
       <c r="C261" s="28" t="n"/>
       <c r="D261" s="27" t="n"/>
@@ -7308,7 +7323,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="38" t="n"/>
+      <c r="A262" s="33" t="n"/>
       <c r="B262" s="28" t="n"/>
       <c r="C262" s="28" t="n"/>
       <c r="D262" s="27" t="n"/>
@@ -7324,7 +7339,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="38" t="n"/>
+      <c r="A263" s="33" t="n"/>
       <c r="B263" s="28" t="n"/>
       <c r="C263" s="28" t="n"/>
       <c r="D263" s="27" t="n"/>
@@ -7340,7 +7355,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="38" t="n"/>
+      <c r="A264" s="33" t="n"/>
       <c r="B264" s="28" t="n"/>
       <c r="C264" s="28" t="n"/>
       <c r="D264" s="27" t="n"/>
@@ -7356,7 +7371,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="38" t="n"/>
+      <c r="A265" s="33" t="n"/>
       <c r="B265" s="28" t="n"/>
       <c r="C265" s="28" t="n"/>
       <c r="D265" s="27" t="n"/>
@@ -7372,7 +7387,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="38" t="n"/>
+      <c r="A266" s="33" t="n"/>
       <c r="B266" s="28" t="n"/>
       <c r="C266" s="28" t="n"/>
       <c r="D266" s="27" t="n"/>
@@ -7388,7 +7403,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="38" t="n"/>
+      <c r="A267" s="33" t="n"/>
       <c r="B267" s="28" t="n"/>
       <c r="C267" s="28" t="n"/>
       <c r="D267" s="27" t="n"/>
@@ -7404,7 +7419,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="38" t="n"/>
+      <c r="A268" s="33" t="n"/>
       <c r="B268" s="28" t="n"/>
       <c r="C268" s="28" t="n"/>
       <c r="D268" s="27" t="n"/>
@@ -7420,7 +7435,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="38" t="n"/>
+      <c r="A269" s="33" t="n"/>
       <c r="B269" s="28" t="n"/>
       <c r="C269" s="28" t="n"/>
       <c r="D269" s="27" t="n"/>
@@ -7436,7 +7451,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="38" t="n"/>
+      <c r="A270" s="33" t="n"/>
       <c r="B270" s="28" t="n"/>
       <c r="C270" s="28" t="n"/>
       <c r="D270" s="27" t="n"/>
@@ -7452,7 +7467,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="38" t="n"/>
+      <c r="A271" s="33" t="n"/>
       <c r="B271" s="28" t="n"/>
       <c r="C271" s="28" t="n"/>
       <c r="D271" s="27" t="n"/>
@@ -7468,7 +7483,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="38" t="n"/>
+      <c r="A272" s="33" t="n"/>
       <c r="B272" s="28" t="n"/>
       <c r="C272" s="28" t="n"/>
       <c r="D272" s="27" t="n"/>
@@ -7484,7 +7499,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="38" t="n"/>
+      <c r="A273" s="33" t="n"/>
       <c r="B273" s="28" t="n"/>
       <c r="C273" s="28" t="n"/>
       <c r="D273" s="27" t="n"/>
@@ -7500,7 +7515,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="38" t="n"/>
+      <c r="A274" s="33" t="n"/>
       <c r="B274" s="28" t="n"/>
       <c r="C274" s="28" t="n"/>
       <c r="D274" s="27" t="n"/>
@@ -7516,7 +7531,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="38" t="n"/>
+      <c r="A275" s="33" t="n"/>
       <c r="B275" s="28" t="n"/>
       <c r="C275" s="28" t="n"/>
       <c r="D275" s="27" t="n"/>
@@ -7532,7 +7547,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="38" t="n"/>
+      <c r="A276" s="33" t="n"/>
       <c r="B276" s="28" t="n"/>
       <c r="C276" s="28" t="n"/>
       <c r="D276" s="27" t="n"/>
@@ -7548,7 +7563,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="38" t="n"/>
+      <c r="A277" s="33" t="n"/>
       <c r="B277" s="28" t="n"/>
       <c r="C277" s="28" t="n"/>
       <c r="D277" s="27" t="n"/>
@@ -7564,7 +7579,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="38" t="n"/>
+      <c r="A278" s="33" t="n"/>
       <c r="B278" s="28" t="n"/>
       <c r="C278" s="28" t="n"/>
       <c r="D278" s="27" t="n"/>
@@ -7580,7 +7595,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="38" t="n"/>
+      <c r="A279" s="33" t="n"/>
       <c r="B279" s="28" t="n"/>
       <c r="C279" s="28" t="n"/>
       <c r="D279" s="27" t="n"/>
@@ -7596,7 +7611,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="38" t="n"/>
+      <c r="A280" s="33" t="n"/>
       <c r="B280" s="28" t="n"/>
       <c r="C280" s="28" t="n"/>
       <c r="D280" s="27" t="n"/>
@@ -7612,7 +7627,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="38" t="n"/>
+      <c r="A281" s="33" t="n"/>
       <c r="B281" s="28" t="n"/>
       <c r="C281" s="28" t="n"/>
       <c r="D281" s="27" t="n"/>
@@ -7628,7 +7643,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="38" t="n"/>
+      <c r="A282" s="33" t="n"/>
       <c r="B282" s="28" t="n"/>
       <c r="C282" s="28" t="n"/>
       <c r="D282" s="27" t="n"/>
@@ -7644,7 +7659,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="38" t="n"/>
+      <c r="A283" s="33" t="n"/>
       <c r="B283" s="28" t="n"/>
       <c r="C283" s="28" t="n"/>
       <c r="D283" s="27" t="n"/>
@@ -7660,7 +7675,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="38" t="n"/>
+      <c r="A284" s="33" t="n"/>
       <c r="B284" s="28" t="n"/>
       <c r="C284" s="28" t="n"/>
       <c r="D284" s="27" t="n"/>
@@ -7676,7 +7691,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="38" t="n"/>
+      <c r="A285" s="33" t="n"/>
       <c r="B285" s="28" t="n"/>
       <c r="C285" s="28" t="n"/>
       <c r="D285" s="27" t="n"/>
@@ -7692,7 +7707,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="38" t="n"/>
+      <c r="A286" s="33" t="n"/>
       <c r="B286" s="28" t="n"/>
       <c r="C286" s="28" t="n"/>
       <c r="D286" s="27" t="n"/>
@@ -7708,7 +7723,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="38" t="n"/>
+      <c r="A287" s="33" t="n"/>
       <c r="B287" s="28" t="n"/>
       <c r="C287" s="28" t="n"/>
       <c r="D287" s="27" t="n"/>
@@ -7724,7 +7739,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="38" t="n"/>
+      <c r="A288" s="33" t="n"/>
       <c r="B288" s="28" t="n"/>
       <c r="C288" s="28" t="n"/>
       <c r="D288" s="27" t="n"/>
@@ -7740,7 +7755,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="38" t="n"/>
+      <c r="A289" s="33" t="n"/>
       <c r="B289" s="28" t="n"/>
       <c r="C289" s="28" t="n"/>
       <c r="D289" s="27" t="n"/>
@@ -7756,7 +7771,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="38" t="n"/>
+      <c r="A290" s="33" t="n"/>
       <c r="B290" s="28" t="n"/>
       <c r="C290" s="28" t="n"/>
       <c r="D290" s="27" t="n"/>
@@ -7772,7 +7787,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="38" t="n"/>
+      <c r="A291" s="33" t="n"/>
       <c r="B291" s="28" t="n"/>
       <c r="C291" s="28" t="n"/>
       <c r="D291" s="27" t="n"/>
@@ -7788,7 +7803,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="38" t="n"/>
+      <c r="A292" s="33" t="n"/>
       <c r="B292" s="28" t="n"/>
       <c r="C292" s="28" t="n"/>
       <c r="D292" s="27" t="n"/>
@@ -7804,7 +7819,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="38" t="n"/>
+      <c r="A293" s="33" t="n"/>
       <c r="B293" s="28" t="n"/>
       <c r="C293" s="28" t="n"/>
       <c r="D293" s="27" t="n"/>
@@ -7820,7 +7835,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="38" t="n"/>
+      <c r="A294" s="33" t="n"/>
       <c r="B294" s="28" t="n"/>
       <c r="C294" s="28" t="n"/>
       <c r="D294" s="27" t="n"/>
@@ -7836,7 +7851,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="38" t="n"/>
+      <c r="A295" s="33" t="n"/>
       <c r="B295" s="28" t="n"/>
       <c r="C295" s="28" t="n"/>
       <c r="D295" s="27" t="n"/>
@@ -7852,7 +7867,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="38" t="n"/>
+      <c r="A296" s="33" t="n"/>
       <c r="B296" s="28" t="n"/>
       <c r="C296" s="28" t="n"/>
       <c r="D296" s="27" t="n"/>
@@ -7868,7 +7883,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="38" t="n"/>
+      <c r="A297" s="33" t="n"/>
       <c r="B297" s="28" t="n"/>
       <c r="C297" s="28" t="n"/>
       <c r="D297" s="27" t="n"/>
@@ -7884,7 +7899,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="38" t="n"/>
+      <c r="A298" s="33" t="n"/>
       <c r="B298" s="28" t="n"/>
       <c r="C298" s="28" t="n"/>
       <c r="D298" s="27" t="n"/>
@@ -7900,7 +7915,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="38" t="n"/>
+      <c r="A299" s="33" t="n"/>
       <c r="B299" s="28" t="n"/>
       <c r="C299" s="28" t="n"/>
       <c r="D299" s="27" t="n"/>
@@ -7916,7 +7931,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="38" t="n"/>
+      <c r="A300" s="33" t="n"/>
       <c r="B300" s="28" t="n"/>
       <c r="C300" s="28" t="n"/>
       <c r="D300" s="27" t="n"/>
@@ -7932,7 +7947,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="38" t="n"/>
+      <c r="A301" s="33" t="n"/>
       <c r="B301" s="28" t="n"/>
       <c r="C301" s="28" t="n"/>
       <c r="D301" s="27" t="n"/>
@@ -7948,7 +7963,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="38" t="n"/>
+      <c r="A302" s="33" t="n"/>
       <c r="B302" s="28" t="n"/>
       <c r="C302" s="28" t="n"/>
       <c r="D302" s="27" t="n"/>
@@ -7964,7 +7979,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="38" t="n"/>
+      <c r="A303" s="33" t="n"/>
       <c r="B303" s="28" t="n"/>
       <c r="C303" s="28" t="n"/>
       <c r="D303" s="27" t="n"/>
@@ -7980,7 +7995,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="38" t="n"/>
+      <c r="A304" s="33" t="n"/>
       <c r="B304" s="28" t="n"/>
       <c r="C304" s="28" t="n"/>
       <c r="D304" s="27" t="n"/>
@@ -7996,7 +8011,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="38" t="n"/>
+      <c r="A305" s="33" t="n"/>
       <c r="B305" s="28" t="n"/>
       <c r="C305" s="28" t="n"/>
       <c r="D305" s="27" t="n"/>
@@ -8012,7 +8027,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="38" t="n"/>
+      <c r="A306" s="33" t="n"/>
       <c r="B306" s="28" t="n"/>
       <c r="C306" s="28" t="n"/>
       <c r="D306" s="27" t="n"/>
@@ -8028,7 +8043,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="38" t="n"/>
+      <c r="A307" s="33" t="n"/>
       <c r="B307" s="28" t="n"/>
       <c r="C307" s="28" t="n"/>
       <c r="D307" s="27" t="n"/>
@@ -8044,7 +8059,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="38" t="n"/>
+      <c r="A308" s="33" t="n"/>
       <c r="B308" s="28" t="n"/>
       <c r="C308" s="28" t="n"/>
       <c r="D308" s="27" t="n"/>
@@ -8060,7 +8075,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="38" t="n"/>
+      <c r="A309" s="33" t="n"/>
       <c r="B309" s="28" t="n"/>
       <c r="C309" s="28" t="n"/>
       <c r="D309" s="27" t="n"/>
@@ -8076,7 +8091,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="38" t="n"/>
+      <c r="A310" s="33" t="n"/>
       <c r="B310" s="28" t="n"/>
       <c r="C310" s="28" t="n"/>
       <c r="D310" s="27" t="n"/>
@@ -8092,7 +8107,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="38" t="n"/>
+      <c r="A311" s="33" t="n"/>
       <c r="B311" s="28" t="n"/>
       <c r="C311" s="28" t="n"/>
       <c r="D311" s="27" t="n"/>
@@ -8108,7 +8123,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="38" t="n"/>
+      <c r="A312" s="33" t="n"/>
       <c r="B312" s="28" t="n"/>
       <c r="C312" s="28" t="n"/>
       <c r="D312" s="27" t="n"/>
@@ -8124,7 +8139,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="38" t="n"/>
+      <c r="A313" s="33" t="n"/>
       <c r="B313" s="28" t="n"/>
       <c r="C313" s="28" t="n"/>
       <c r="D313" s="27" t="n"/>
@@ -8140,7 +8155,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="38" t="n"/>
+      <c r="A314" s="33" t="n"/>
       <c r="B314" s="28" t="n"/>
       <c r="C314" s="28" t="n"/>
       <c r="D314" s="27" t="n"/>
@@ -8156,7 +8171,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="38" t="n"/>
+      <c r="A315" s="33" t="n"/>
       <c r="B315" s="28" t="n"/>
       <c r="C315" s="28" t="n"/>
       <c r="D315" s="27" t="n"/>
@@ -8172,7 +8187,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="38" t="n"/>
+      <c r="A316" s="33" t="n"/>
       <c r="B316" s="28" t="n"/>
       <c r="C316" s="28" t="n"/>
       <c r="D316" s="27" t="n"/>
@@ -8188,7 +8203,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="38" t="n"/>
+      <c r="A317" s="33" t="n"/>
       <c r="B317" s="28" t="n"/>
       <c r="C317" s="28" t="n"/>
       <c r="D317" s="27" t="n"/>
@@ -8204,7 +8219,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="38" t="n"/>
+      <c r="A318" s="33" t="n"/>
       <c r="B318" s="28" t="n"/>
       <c r="C318" s="28" t="n"/>
       <c r="D318" s="27" t="n"/>
@@ -8220,7 +8235,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="38" t="n"/>
+      <c r="A319" s="33" t="n"/>
       <c r="B319" s="28" t="n"/>
       <c r="C319" s="28" t="n"/>
       <c r="D319" s="27" t="n"/>
@@ -8236,7 +8251,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="38" t="n"/>
+      <c r="A320" s="33" t="n"/>
       <c r="B320" s="28" t="n"/>
       <c r="C320" s="28" t="n"/>
       <c r="D320" s="27" t="n"/>
@@ -8252,7 +8267,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="38" t="n"/>
+      <c r="A321" s="33" t="n"/>
       <c r="B321" s="28" t="n"/>
       <c r="C321" s="28" t="n"/>
       <c r="D321" s="27" t="n"/>
@@ -8268,7 +8283,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="38" t="n"/>
+      <c r="A322" s="33" t="n"/>
       <c r="B322" s="28" t="n"/>
       <c r="C322" s="28" t="n"/>
       <c r="D322" s="27" t="n"/>
@@ -8284,7 +8299,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="38" t="n"/>
+      <c r="A323" s="33" t="n"/>
       <c r="B323" s="28" t="n"/>
       <c r="C323" s="28" t="n"/>
       <c r="D323" s="27" t="n"/>
@@ -8300,7 +8315,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="38" t="n"/>
+      <c r="A324" s="33" t="n"/>
       <c r="B324" s="28" t="n"/>
       <c r="C324" s="28" t="n"/>
       <c r="D324" s="27" t="n"/>
@@ -8316,7 +8331,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="38" t="n"/>
+      <c r="A325" s="33" t="n"/>
       <c r="B325" s="28" t="n"/>
       <c r="C325" s="28" t="n"/>
       <c r="D325" s="27" t="n"/>
@@ -8332,7 +8347,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="38" t="n"/>
+      <c r="A326" s="33" t="n"/>
       <c r="B326" s="28" t="n"/>
       <c r="C326" s="28" t="n"/>
       <c r="D326" s="27" t="n"/>
@@ -8348,7 +8363,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="38" t="n"/>
+      <c r="A327" s="33" t="n"/>
       <c r="B327" s="28" t="n"/>
       <c r="C327" s="28" t="n"/>
       <c r="D327" s="27" t="n"/>
@@ -8364,7 +8379,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="38" t="n"/>
+      <c r="A328" s="33" t="n"/>
       <c r="B328" s="28" t="n"/>
       <c r="C328" s="28" t="n"/>
       <c r="D328" s="27" t="n"/>
@@ -8380,7 +8395,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="38" t="n"/>
+      <c r="A329" s="33" t="n"/>
       <c r="B329" s="28" t="n"/>
       <c r="C329" s="28" t="n"/>
       <c r="D329" s="27" t="n"/>
@@ -8396,7 +8411,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="38" t="n"/>
+      <c r="A330" s="33" t="n"/>
       <c r="B330" s="28" t="n"/>
       <c r="C330" s="28" t="n"/>
       <c r="D330" s="27" t="n"/>
@@ -8412,7 +8427,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="38" t="n"/>
+      <c r="A331" s="33" t="n"/>
       <c r="B331" s="28" t="n"/>
       <c r="C331" s="28" t="n"/>
       <c r="D331" s="27" t="n"/>
@@ -8428,7 +8443,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="38" t="n"/>
+      <c r="A332" s="33" t="n"/>
       <c r="B332" s="28" t="n"/>
       <c r="C332" s="28" t="n"/>
       <c r="D332" s="27" t="n"/>
@@ -8444,7 +8459,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="38" t="n"/>
+      <c r="A333" s="33" t="n"/>
       <c r="B333" s="28" t="n"/>
       <c r="C333" s="28" t="n"/>
       <c r="D333" s="27" t="n"/>
@@ -8460,7 +8475,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="38" t="n"/>
+      <c r="A334" s="33" t="n"/>
       <c r="B334" s="28" t="n"/>
       <c r="C334" s="28" t="n"/>
       <c r="D334" s="27" t="n"/>
@@ -8476,7 +8491,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="38" t="n"/>
+      <c r="A335" s="33" t="n"/>
       <c r="B335" s="28" t="n"/>
       <c r="C335" s="28" t="n"/>
       <c r="D335" s="27" t="n"/>
@@ -8492,7 +8507,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="38" t="n"/>
+      <c r="A336" s="33" t="n"/>
       <c r="B336" s="28" t="n"/>
       <c r="C336" s="28" t="n"/>
       <c r="D336" s="27" t="n"/>
@@ -8508,7 +8523,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="38" t="n"/>
+      <c r="A337" s="33" t="n"/>
       <c r="B337" s="28" t="n"/>
       <c r="C337" s="28" t="n"/>
       <c r="D337" s="27" t="n"/>
@@ -8524,7 +8539,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="38" t="n"/>
+      <c r="A338" s="33" t="n"/>
       <c r="B338" s="28" t="n"/>
       <c r="C338" s="28" t="n"/>
       <c r="D338" s="27" t="n"/>
@@ -8540,7 +8555,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="38" t="n"/>
+      <c r="A339" s="33" t="n"/>
       <c r="B339" s="28" t="n"/>
       <c r="C339" s="28" t="n"/>
       <c r="D339" s="27" t="n"/>
@@ -8556,7 +8571,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="38" t="n"/>
+      <c r="A340" s="33" t="n"/>
       <c r="B340" s="28" t="n"/>
       <c r="C340" s="28" t="n"/>
       <c r="D340" s="27" t="n"/>
@@ -8572,7 +8587,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="38" t="n"/>
+      <c r="A341" s="33" t="n"/>
       <c r="B341" s="28" t="n"/>
       <c r="C341" s="28" t="n"/>
       <c r="D341" s="27" t="n"/>
@@ -8588,7 +8603,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="38" t="n"/>
+      <c r="A342" s="33" t="n"/>
       <c r="B342" s="28" t="n"/>
       <c r="C342" s="28" t="n"/>
       <c r="D342" s="27" t="n"/>
@@ -8604,7 +8619,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="38" t="n"/>
+      <c r="A343" s="33" t="n"/>
       <c r="B343" s="28" t="n"/>
       <c r="C343" s="28" t="n"/>
       <c r="D343" s="27" t="n"/>
@@ -8620,7 +8635,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="38" t="n"/>
+      <c r="A344" s="33" t="n"/>
       <c r="B344" s="28" t="n"/>
       <c r="C344" s="28" t="n"/>
       <c r="D344" s="27" t="n"/>
@@ -8636,7 +8651,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="38" t="n"/>
+      <c r="A345" s="33" t="n"/>
       <c r="B345" s="28" t="n"/>
       <c r="C345" s="28" t="n"/>
       <c r="D345" s="27" t="n"/>
@@ -8652,7 +8667,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="38" t="n"/>
+      <c r="A346" s="33" t="n"/>
       <c r="B346" s="28" t="n"/>
       <c r="C346" s="28" t="n"/>
       <c r="D346" s="27" t="n"/>
@@ -8668,7 +8683,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="38" t="n"/>
+      <c r="A347" s="33" t="n"/>
       <c r="B347" s="28" t="n"/>
       <c r="C347" s="28" t="n"/>
       <c r="D347" s="27" t="n"/>
@@ -8684,7 +8699,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="38" t="n"/>
+      <c r="A348" s="33" t="n"/>
       <c r="B348" s="28" t="n"/>
       <c r="C348" s="28" t="n"/>
       <c r="D348" s="27" t="n"/>
@@ -8700,7 +8715,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="38" t="n"/>
+      <c r="A349" s="33" t="n"/>
       <c r="B349" s="28" t="n"/>
       <c r="C349" s="28" t="n"/>
       <c r="D349" s="27" t="n"/>
@@ -8716,7 +8731,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="38" t="n"/>
+      <c r="A350" s="33" t="n"/>
       <c r="B350" s="28" t="n"/>
       <c r="C350" s="28" t="n"/>
       <c r="D350" s="27" t="n"/>
@@ -8732,7 +8747,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="38" t="n"/>
+      <c r="A351" s="33" t="n"/>
       <c r="B351" s="28" t="n"/>
       <c r="C351" s="28" t="n"/>
       <c r="D351" s="27" t="n"/>
@@ -8748,7 +8763,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="38" t="n"/>
+      <c r="A352" s="33" t="n"/>
       <c r="B352" s="28" t="n"/>
       <c r="C352" s="28" t="n"/>
       <c r="D352" s="27" t="n"/>
@@ -8764,7 +8779,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="38" t="n"/>
+      <c r="A353" s="33" t="n"/>
       <c r="B353" s="28" t="n"/>
       <c r="C353" s="28" t="n"/>
       <c r="D353" s="27" t="n"/>
@@ -8780,7 +8795,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="38" t="n"/>
+      <c r="A354" s="33" t="n"/>
       <c r="B354" s="28" t="n"/>
       <c r="C354" s="28" t="n"/>
       <c r="D354" s="27" t="n"/>
@@ -8796,7 +8811,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="38" t="n"/>
+      <c r="A355" s="33" t="n"/>
       <c r="B355" s="28" t="n"/>
       <c r="C355" s="28" t="n"/>
       <c r="D355" s="27" t="n"/>
@@ -8812,7 +8827,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="38" t="n"/>
+      <c r="A356" s="33" t="n"/>
       <c r="B356" s="28" t="n"/>
       <c r="C356" s="28" t="n"/>
       <c r="D356" s="27" t="n"/>
@@ -8828,7 +8843,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="38" t="n"/>
+      <c r="A357" s="33" t="n"/>
       <c r="B357" s="28" t="n"/>
       <c r="C357" s="28" t="n"/>
       <c r="D357" s="27" t="n"/>
@@ -8844,7 +8859,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="38" t="n"/>
+      <c r="A358" s="33" t="n"/>
       <c r="B358" s="28" t="n"/>
       <c r="C358" s="28" t="n"/>
       <c r="D358" s="27" t="n"/>
@@ -8860,7 +8875,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="38" t="n"/>
+      <c r="A359" s="33" t="n"/>
       <c r="B359" s="28" t="n"/>
       <c r="C359" s="28" t="n"/>
       <c r="D359" s="27" t="n"/>
@@ -8876,7 +8891,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="38" t="n"/>
+      <c r="A360" s="33" t="n"/>
       <c r="B360" s="28" t="n"/>
       <c r="C360" s="28" t="n"/>
       <c r="D360" s="27" t="n"/>
@@ -8892,7 +8907,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="38" t="n"/>
+      <c r="A361" s="33" t="n"/>
       <c r="B361" s="28" t="n"/>
       <c r="C361" s="28" t="n"/>
       <c r="D361" s="27" t="n"/>
@@ -8908,7 +8923,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="38" t="n"/>
+      <c r="A362" s="33" t="n"/>
       <c r="B362" s="28" t="n"/>
       <c r="C362" s="28" t="n"/>
       <c r="D362" s="27" t="n"/>
@@ -8924,7 +8939,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="38" t="n"/>
+      <c r="A363" s="33" t="n"/>
       <c r="B363" s="28" t="n"/>
       <c r="C363" s="28" t="n"/>
       <c r="D363" s="27" t="n"/>
@@ -8940,7 +8955,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="38" t="n"/>
+      <c r="A364" s="33" t="n"/>
       <c r="B364" s="28" t="n"/>
       <c r="C364" s="28" t="n"/>
       <c r="D364" s="27" t="n"/>
@@ -8956,7 +8971,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="38" t="n"/>
+      <c r="A365" s="33" t="n"/>
       <c r="B365" s="28" t="n"/>
       <c r="C365" s="28" t="n"/>
       <c r="D365" s="27" t="n"/>
@@ -8972,7 +8987,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="38" t="n"/>
+      <c r="A366" s="33" t="n"/>
       <c r="B366" s="28" t="n"/>
       <c r="C366" s="28" t="n"/>
       <c r="D366" s="27" t="n"/>
@@ -8988,7 +9003,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="38" t="n"/>
+      <c r="A367" s="33" t="n"/>
       <c r="B367" s="28" t="n"/>
       <c r="C367" s="28" t="n"/>
       <c r="D367" s="27" t="n"/>
@@ -9004,7 +9019,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="38" t="n"/>
+      <c r="A368" s="33" t="n"/>
       <c r="B368" s="28" t="n"/>
       <c r="C368" s="28" t="n"/>
       <c r="D368" s="27" t="n"/>
@@ -9020,7 +9035,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="38" t="n"/>
+      <c r="A369" s="33" t="n"/>
       <c r="B369" s="28" t="n"/>
       <c r="C369" s="28" t="n"/>
       <c r="D369" s="27" t="n"/>
@@ -9036,7 +9051,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="38" t="n"/>
+      <c r="A370" s="33" t="n"/>
       <c r="B370" s="28" t="n"/>
       <c r="C370" s="28" t="n"/>
       <c r="D370" s="27" t="n"/>
@@ -9052,7 +9067,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="38" t="n"/>
+      <c r="A371" s="33" t="n"/>
       <c r="B371" s="28" t="n"/>
       <c r="C371" s="28" t="n"/>
       <c r="D371" s="27" t="n"/>
@@ -9068,7 +9083,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="38" t="n"/>
+      <c r="A372" s="33" t="n"/>
       <c r="B372" s="28" t="n"/>
       <c r="C372" s="28" t="n"/>
       <c r="D372" s="27" t="n"/>
@@ -9084,7 +9099,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="38" t="n"/>
+      <c r="A373" s="33" t="n"/>
       <c r="B373" s="28" t="n"/>
       <c r="C373" s="28" t="n"/>
       <c r="D373" s="27" t="n"/>
@@ -9100,7 +9115,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="38" t="n"/>
+      <c r="A374" s="33" t="n"/>
       <c r="B374" s="28" t="n"/>
       <c r="C374" s="28" t="n"/>
       <c r="D374" s="27" t="n"/>
@@ -9116,7 +9131,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="38" t="n"/>
+      <c r="A375" s="33" t="n"/>
       <c r="B375" s="28" t="n"/>
       <c r="C375" s="28" t="n"/>
       <c r="D375" s="27" t="n"/>
@@ -9132,7 +9147,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="38" t="n"/>
+      <c r="A376" s="33" t="n"/>
       <c r="B376" s="28" t="n"/>
       <c r="C376" s="28" t="n"/>
       <c r="D376" s="27" t="n"/>
@@ -9148,7 +9163,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="38" t="n"/>
+      <c r="A377" s="33" t="n"/>
       <c r="B377" s="28" t="n"/>
       <c r="C377" s="28" t="n"/>
       <c r="D377" s="27" t="n"/>
@@ -9164,7 +9179,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="38" t="n"/>
+      <c r="A378" s="33" t="n"/>
       <c r="B378" s="28" t="n"/>
       <c r="C378" s="28" t="n"/>
       <c r="D378" s="27" t="n"/>
@@ -9180,7 +9195,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="38" t="n"/>
+      <c r="A379" s="33" t="n"/>
       <c r="B379" s="28" t="n"/>
       <c r="C379" s="28" t="n"/>
       <c r="D379" s="27" t="n"/>
@@ -9196,7 +9211,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="38" t="n"/>
+      <c r="A380" s="33" t="n"/>
       <c r="B380" s="28" t="n"/>
       <c r="C380" s="28" t="n"/>
       <c r="D380" s="27" t="n"/>
@@ -9212,7 +9227,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="38" t="n"/>
+      <c r="A381" s="33" t="n"/>
       <c r="B381" s="28" t="n"/>
       <c r="C381" s="28" t="n"/>
       <c r="D381" s="27" t="n"/>
@@ -9228,7 +9243,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="38" t="n"/>
+      <c r="A382" s="33" t="n"/>
       <c r="B382" s="28" t="n"/>
       <c r="C382" s="28" t="n"/>
       <c r="D382" s="27" t="n"/>
@@ -9244,7 +9259,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="38" t="n"/>
+      <c r="A383" s="33" t="n"/>
       <c r="B383" s="28" t="n"/>
       <c r="C383" s="28" t="n"/>
       <c r="D383" s="27" t="n"/>
@@ -9260,7 +9275,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="38" t="n"/>
+      <c r="A384" s="33" t="n"/>
       <c r="B384" s="28" t="n"/>
       <c r="C384" s="28" t="n"/>
       <c r="D384" s="27" t="n"/>
@@ -9276,7 +9291,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="38" t="n"/>
+      <c r="A385" s="33" t="n"/>
       <c r="B385" s="28" t="n"/>
       <c r="C385" s="28" t="n"/>
       <c r="D385" s="27" t="n"/>
@@ -9292,7 +9307,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="38" t="n"/>
+      <c r="A386" s="33" t="n"/>
       <c r="B386" s="28" t="n"/>
       <c r="C386" s="28" t="n"/>
       <c r="D386" s="27" t="n"/>
@@ -9308,7 +9323,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="38" t="n"/>
+      <c r="A387" s="33" t="n"/>
       <c r="B387" s="28" t="n"/>
       <c r="C387" s="28" t="n"/>
       <c r="D387" s="27" t="n"/>
@@ -9324,7 +9339,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="38" t="n"/>
+      <c r="A388" s="33" t="n"/>
       <c r="B388" s="28" t="n"/>
       <c r="C388" s="28" t="n"/>
       <c r="D388" s="27" t="n"/>
@@ -9340,7 +9355,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="38" t="n"/>
+      <c r="A389" s="33" t="n"/>
       <c r="B389" s="28" t="n"/>
       <c r="C389" s="28" t="n"/>
       <c r="D389" s="27" t="n"/>
@@ -9356,7 +9371,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="38" t="n"/>
+      <c r="A390" s="33" t="n"/>
       <c r="B390" s="28" t="n"/>
       <c r="C390" s="28" t="n"/>
       <c r="D390" s="27" t="n"/>
@@ -9372,7 +9387,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="38" t="n"/>
+      <c r="A391" s="33" t="n"/>
       <c r="B391" s="28" t="n"/>
       <c r="C391" s="28" t="n"/>
       <c r="D391" s="27" t="n"/>
@@ -9388,7 +9403,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="38" t="n"/>
+      <c r="A392" s="33" t="n"/>
       <c r="B392" s="28" t="n"/>
       <c r="C392" s="28" t="n"/>
       <c r="D392" s="27" t="n"/>
@@ -9404,7 +9419,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="38" t="n"/>
+      <c r="A393" s="33" t="n"/>
       <c r="B393" s="28" t="n"/>
       <c r="C393" s="28" t="n"/>
       <c r="D393" s="27" t="n"/>
@@ -9420,7 +9435,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="38" t="n"/>
+      <c r="A394" s="33" t="n"/>
       <c r="B394" s="28" t="n"/>
       <c r="C394" s="28" t="n"/>
       <c r="D394" s="27" t="n"/>
@@ -9436,7 +9451,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="38" t="n"/>
+      <c r="A395" s="33" t="n"/>
       <c r="B395" s="28" t="n"/>
       <c r="C395" s="28" t="n"/>
       <c r="D395" s="27" t="n"/>
@@ -9452,7 +9467,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="38" t="n"/>
+      <c r="A396" s="33" t="n"/>
       <c r="B396" s="28" t="n"/>
       <c r="C396" s="28" t="n"/>
       <c r="D396" s="27" t="n"/>
@@ -9468,7 +9483,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="38" t="n"/>
+      <c r="A397" s="33" t="n"/>
       <c r="B397" s="28" t="n"/>
       <c r="C397" s="28" t="n"/>
       <c r="D397" s="27" t="n"/>
@@ -9484,7 +9499,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="38" t="n"/>
+      <c r="A398" s="33" t="n"/>
       <c r="B398" s="28" t="n"/>
       <c r="C398" s="28" t="n"/>
       <c r="D398" s="27" t="n"/>
@@ -9500,7 +9515,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="38" t="n"/>
+      <c r="A399" s="33" t="n"/>
       <c r="B399" s="28" t="n"/>
       <c r="C399" s="28" t="n"/>
       <c r="D399" s="27" t="n"/>
@@ -9516,7 +9531,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="38" t="n"/>
+      <c r="A400" s="33" t="n"/>
       <c r="B400" s="28" t="n"/>
       <c r="C400" s="28" t="n"/>
       <c r="D400" s="27" t="n"/>
@@ -9532,7 +9547,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="38" t="n"/>
+      <c r="A401" s="33" t="n"/>
       <c r="B401" s="28" t="n"/>
       <c r="C401" s="28" t="n"/>
       <c r="D401" s="27" t="n"/>
@@ -9548,7 +9563,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="38" t="n"/>
+      <c r="A402" s="33" t="n"/>
       <c r="B402" s="28" t="n"/>
       <c r="C402" s="28" t="n"/>
       <c r="D402" s="27" t="n"/>
@@ -9564,7 +9579,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="38" t="n"/>
+      <c r="A403" s="33" t="n"/>
       <c r="B403" s="28" t="n"/>
       <c r="C403" s="28" t="n"/>
       <c r="D403" s="27" t="n"/>
@@ -9580,7 +9595,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="38" t="n"/>
+      <c r="A404" s="33" t="n"/>
       <c r="B404" s="28" t="n"/>
       <c r="C404" s="28" t="n"/>
       <c r="D404" s="27" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/11-pro-labore.xlsx
@@ -748,6 +748,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -876,7 +877,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
